--- a/extraction/penford.xlsx
+++ b/extraction/penford.xlsx
@@ -13,9 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deal facts" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Deal ledger'!$A$1:$V$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Deal ledger'!$A$1:$V$53</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Rounds'!$A$1:$J$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Questions'!$A$1:$G$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Questions'!$A$1:$G$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Deal facts'!$A$1:$B$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -439,27 +439,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V49"/>
+  <dimension ref="A1:V53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="7" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
     <col width="9" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="7" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
     <col width="8" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
-    <col width="55" customWidth="1" min="17" max="17"/>
-    <col width="9" customWidth="1" min="18" max="18"/>
+    <col width="60" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
     <col width="14" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
     <col width="12" customWidth="1" min="21" max="21"/>
@@ -614,12 +614,12 @@
       <c r="O2" s="2" t="n"/>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>SEACOR, a Penford shareholder with a board representative (Mr. Behrens), amends its Schedule 13D announcing intent to nominate four directors at the next annual meeting; nominees named 08/19. Later signs voting and support agreement (#38, #45).</t>
+          <t>SEACOR (about 9.28% holder; its representative Mr. Behrens sits on the board) amended its Schedule 13D announcing a board nomination contest for four seats; nominees named in 08/19/2014 amendment. Later signs voting and support agreement (#49).</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>“SEACOR stated its intent to nominate four candidates for election as directors of our board at Penford’s next annual meeting of shareholders” (p. 24)</t>
+          <t>SEACOR stated its intent to nominate four candidates for election as directors of our board at Penford’s next annual meeting of shareholders (p. 24)</t>
         </is>
       </c>
       <c r="R2" s="2" t="n"/>
@@ -676,12 +676,12 @@
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>First contact: CEO Gordon left voicemail 07/08 seeking unexplained meeting; at 07/17 lunch said Ingredion wants to acquire Penford. No price; cited 52-week high of about $16.00 and current price of about $12.00 (historical prices, not an offer).</t>
+          <t>First contact: Ingredion CEO Gordon left voicemail 07/08/2014 seeking a meeting, purpose unstated. At 07/17 lunch she stated interest in acquiring Penford, cited no price; noted 52-week high about $16.00 and trading price about $12.00. CFO meeting 07/19 also named no price.</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>“Ms. Gordon advised Mr. Malkoski of Ingredion’s interest in acquiring Penford” (p. 24)</t>
+          <t>Ms. Gordon advised Mr. Malkoski of Ingredion’s interest in acquiring Penford (p. 24)</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>07/20/2014</t>
+          <t>effective 07/20/2014</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -742,12 +742,12 @@
       <c r="O4" s="2" t="n"/>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Entry. Secrecy Agreement executed after the 07/19 CFO meeting, effective 07/20; limited exchange of confidential information, confidentiality of talks. Superseded by #12.</t>
+          <t>Secrecy Agreement for limited exchange of confidential information; executed 'subsequently' to the 07/19 meeting, effective 07/20; execution day not stated, so Date to runs to its supersession on 08/21 (#13). Ingredion's entry.</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>“Penford and Ingredion executed a Secrecy Agreement, effective as of July 20, 2014, providing for limited exchange of confidential information” (p. 24)</t>
+          <t>Penford and Ingredion executed a Secrecy Agreement, effective as of July 20, 2014, providing for limited exchange of confidential information (p. 24)</t>
         </is>
       </c>
       <c r="R4" s="2" t="n"/>
@@ -759,7 +759,7 @@
         <v>41840</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>41840</v>
+        <v>41872</v>
       </c>
     </row>
     <row r="5">
@@ -798,12 +798,12 @@
       <c r="O5" s="2" t="n"/>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Penford’s legal counsel; first seen acting at the 07/24 Executive Committee meeting. Advised throughout and reviewed fiduciary duties 08/28 and 10/14.</t>
+          <t>Penford's legal counsel; earliest shown acting at the 07/24/2014 Executive Committee meeting. Advised board on fiduciary duties and negotiated the merger agreement.</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>“representatives of Perkins Coie LLP (referred to as Perkins Coie), Penford’s legal counsel, were present” (p. 24)</t>
+          <t>representatives of Perkins Coie LLP (referred to as Perkins Coie), Penford’s legal counsel, were present (p. 25)</t>
         </is>
       </c>
       <c r="R5" s="2" t="n"/>
@@ -854,12 +854,12 @@
       <c r="O6" s="2" t="n"/>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>Penford’s financial adviser (sole one named): Executive Committee directs its retention to advise on shareholder matters and evaluate strategic alternatives; engagement letter executed 09/11/2014. Deutsche Bank Securities Inc. gave the fairness opinion 10/14.</t>
+          <t>Penford's financial adviser. Executive Committee directed management to retain it (interviews held earlier in July) to advise on shareholder matters and strategic alternatives; engagement letter executed 09/11/2014. Delivered fairness opinion 10/14/2014.</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>“the Executive Committee directed management to proceed to retain Deutsche Bank as the Company’s financial advisor” (p. 24)</t>
+          <t>the Executive Committee directed management to proceed to retain Deutsche Bank as the Company’s financial advisor (p. 25)</t>
         </is>
       </c>
       <c r="R6" s="2" t="n"/>
@@ -932,12 +932,12 @@
       <c r="O7" s="2" t="n"/>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Diligence open per narrative: management presentation 08/21; data room early September. Oral, at meeting: CFO says Ingredion prepared to propose and $17.00 fully diluted could likely win its board’s support. Malkoski: probably not enough for Penford’s board.</t>
+          <t>Unclear: no conditions reported; diligence not yet begun. Oral: CFO Fortnum said Ingredion prepared to submit a proposal and $17.00 fully diluted could likely get Ingredion board support. Malkoski said probably too low. Cash not stated.</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>“Mr. Fortnum suggested that a price of $17.00 per share on a fully diluted basis could likely get support from Ingredion’s board” (p. 25)</t>
+          <t>Mr. Fortnum suggested that a price of $17.00 per share on a fully diluted basis could likely get support from Ingredion’s board (p. 25)</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="O8" s="2" t="n"/>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Diligence open per narrative: management presentation 08/21; data room early September. Letter giving an “indicative valuation” in cash, fully diluted; Deutsche Bank calls it non-binding (p. 26). Board: not full value (told 08/14). Ref: $12.10 close 08/08/2014; 49% premium.</t>
+          <t>Unclear: letter states no conditions; diligence then followed (#13, #17). Indicative $18.00 cash, fully diluted, for all stock; board called it non-binding. Ref: $12.10 close 08/08/2014; 49% premium.</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>“providing an indicative valuation of $18.00 per share in cash for all of the outstanding capital stock of Penford on a fully diluted basis” (p. 25)</t>
+          <t>providing an indicative valuation of $18.00 per share in cash for all of the outstanding capital stock of Penford on a fully diluted basis (p. 25)</t>
         </is>
       </c>
       <c r="R8" s="2" t="n"/>
@@ -1076,19 +1076,15 @@
       <c r="O9" s="2" t="n"/>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>First contact: representative of Party A (“a company in the industry”) emailed 08/01 for a call; at 08/11 CEO meeting Party A informally raised acquiring or combining, valuing Penford only at a typical premium to trading price on trailing results. No price.</t>
+          <t>First contact: representative of Party A (a company in the industry) emailed 08/01/2014 asking for a call. At 08/11 CEO meeting Party A informally raised interest in acquiring or combining; would value only at a typical premium to trading price, not strategic plan. No price.</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>“Party A’s Chief Executive Officer also informally discussed Party A’s potential interest in acquiring or combining with Penford” (p. 26)</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
+          <t>Party A’s Chief Executive Officer also informally discussed Party A’s potential interest in acquiring or combining with Penford (p. 26)</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="n"/>
       <c r="S9" s="2" t="n"/>
       <c r="T9" s="3" t="n">
         <v>41862</v>
@@ -1142,12 +1138,12 @@
       <c r="O10" s="2" t="n"/>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Executive Committee (08/11), after Deutsche Bank named SEACOR as a possible acquirer, had Chairman Hatfield ask SEACOR’s board representative Behrens; SEACOR not interested “at that time”, reconfirmed at 08/13 board. Never entered. Filing does not describe SEACOR’s business.</t>
+          <t>Executive Committee (08/11) had Chairman Hatfield ask SEACOR's board representative Behrens, as Deutsche Bank identified SEACOR as a possible acquirer. SEACOR not interested 'at that time'; reconfirmed 08/13. No NDA; never entered. Type not described in filing.</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>“Mr. Behrens stated that SEACOR was not interested in participating in any potential sale process at that time” (p. 26)</t>
+          <t>Mr. Behrens stated that SEACOR was not interested in participating in any potential sale process at that time (p. 26)</t>
         </is>
       </c>
       <c r="R10" s="2" t="n"/>
@@ -1198,19 +1194,15 @@
       <c r="O11" s="2" t="n"/>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Board directs management to investigate and develop the Ingredion proposal (#7) and share information to raise the price; a “market check” of other counterparties contemplated only if progress is made and an acceptable price received. Executive Committee took similar step 08/11.</t>
+          <t>Board directed management to further investigate and develop Ingredion's proposal (Executive Committee reached the same view 08/11). A 'market check' of other counterparties was contemplated only if progress was made and an acceptable price received.</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>“the board members present at the meeting unanimously directed management to proceed with further investigation and development of the proposal from Ingredion” (p. 26)</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>Q3</t>
-        </is>
-      </c>
+          <t>the board members present at the meeting unanimously directed management to proceed with further investigation and development of the proposal from Ingredion (p. 26)</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="n"/>
       <c r="S11" s="2" t="n"/>
       <c r="T11" s="3" t="n">
         <v>41864</v>
@@ -1233,17 +1225,13 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Ingredion</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Penford</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n"/>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Exclusivity changed</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
@@ -1257,19 +1245,17 @@
       <c r="J12" s="2" t="n"/>
       <c r="K12" s="2" t="n"/>
       <c r="L12" s="2" t="n"/>
-      <c r="M12" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M12" s="2" t="n"/>
       <c r="N12" s="2" t="n"/>
       <c r="O12" s="2" t="n"/>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>Requested and refused: Ingredion asks about exclusive negotiations; Penford declines, having told it $18.00 did not reflect full value and offered information and a management presentation. Penford declined exclusivity again 08/20–08/21.</t>
+          <t>Rejected $18.00 as not reflecting full value; board authorized engagement and information sharing so Ingredion would raise its price; management presentation set for 08/21 and diligence process discussed.</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>“Mr. Malkoski indicated that the current status of negotiations and the proposed price did not justify providing exclusivity” (p. 27)</t>
+          <t>the board authorized management to engage with Ingredion and provide additional information regarding the Company (p. 27)</t>
         </is>
       </c>
       <c r="R12" s="2" t="n"/>
@@ -1290,7 +1276,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>08/21/2014</t>
+          <t>08/14/2014</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1305,7 +1291,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>NDA signed</t>
+          <t>Exclusivity changed</t>
         </is>
       </c>
       <c r="F13" s="2" t="n">
@@ -1326,24 +1312,24 @@
       <c r="O13" s="2" t="n"/>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Nondisclosure and standstill agreement, supersedes #3; negotiated 08/15–08/21 and signed immediately before the management presentation (#14). No new entry.</t>
+          <t>Requested: Ingredion asked whether Penford would consider exclusive negotiations; Penford declined as status and price did not justify it. Penford again declined exclusivity on 08/20–08/21/2014. No exclusivity was ever granted.</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>“Ingredion and Penford executed a nondisclosure and standstill agreement that superseded the prior Secrecy Agreement” (p. 27)</t>
+          <t>Mr. Malkoski indicated that the current status of negotiations and the proposed price did not justify providing exclusivity (p. 27)</t>
         </is>
       </c>
       <c r="R13" s="2" t="n"/>
       <c r="S13" s="2" t="n"/>
       <c r="T13" s="3" t="n">
-        <v>41872</v>
+        <v>41865</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>41872</v>
+        <v>41865</v>
       </c>
       <c r="V13" s="3" t="n">
-        <v>41872</v>
+        <v>41865</v>
       </c>
     </row>
     <row r="14">
@@ -1357,13 +1343,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>J.P. Morgan Securities</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="n"/>
+          <t>Ingredion</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Adviser</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
@@ -1377,17 +1367,19 @@
       <c r="J14" s="2" t="n"/>
       <c r="K14" s="2" t="n"/>
       <c r="L14" s="2" t="n"/>
-      <c r="M14" s="2" t="n"/>
+      <c r="M14" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N14" s="2" t="n"/>
       <c r="O14" s="2" t="n"/>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Ingredion’s financial adviser; first seen acting at the 08/21 management presentation. Sent Ingredion’s initial draft merger agreement 09/06.</t>
+          <t>Executed nondisclosure and standstill agreement superseding the Secrecy Agreement (#3); same day, management presentation to Ingredion and J.P. Morgan with historical results and financial projections. Ingredion was then the only party under NDA.</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>“representatives of J.P. Morgan Securities, Ingredion’s financial advisor” (p. 27)</t>
+          <t>On August 21, 2014, Ingredion and Penford executed a nondisclosure and standstill agreement that superseded the prior Secrecy Agreement. (p. 27)</t>
         </is>
       </c>
       <c r="R14" s="2" t="n"/>
@@ -1413,17 +1405,13 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Ingredion</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>J.P. Morgan Securities</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n"/>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Adviser</t>
         </is>
       </c>
       <c r="F15" s="2" t="n">
@@ -1437,19 +1425,17 @@
       <c r="J15" s="2" t="n"/>
       <c r="K15" s="2" t="n"/>
       <c r="L15" s="2" t="n"/>
-      <c r="M15" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M15" s="2" t="n"/>
       <c r="N15" s="2" t="n"/>
       <c r="O15" s="2" t="n"/>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>Information given: management presentation to Ingredion’s CEO, CFO, senior management and J.P. Morgan, including financial projections (the Strategic Plan, last updated 08/28, per p. 43). Ingredion was then the only party under NDA. Initial diligence request list followed 08/26.</t>
+          <t>Ingredion's financial adviser; earliest shown acting at the 08/21/2014 management presentation. Delivered Ingredion's draft merger agreement 09/06 (#18).</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>“This presentation provided information regarding Penford’s operations, corporate strategy, business segments, product applications and technologies, end markets, supply chain and manufacturing, facilities, historical financial performance and financial projections” (p. 27)</t>
+          <t>representatives of J.P. Morgan Securities, Ingredion’s financial advisor (p. 27)</t>
         </is>
       </c>
       <c r="R15" s="2" t="n"/>
@@ -1500,12 +1486,12 @@
       <c r="O16" s="2" t="n"/>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Board directs continued negotiation and diligence with Ingredion and authorizes a Deutsche Bank “market check”: CEOs of selected companies to be queried, substantive information only under NDA.</t>
+          <t>Board directed continued negotiation and diligence with Ingredion and authorized Deutsche Bank to run a 'market check': CEO-level inquiries to selected companies, substantive information only under an acceptable NDA. Launches the outreach in #16.</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>“The board also authorized management and Deutsche Bank to proceed with the market check process as described at the meeting.” (p. 27)</t>
+          <t>The board also authorized management and Deutsche Bank to proceed with the market check process as described at the meeting. (p. 27)</t>
         </is>
       </c>
       <c r="R16" s="2" t="n"/>
@@ -1526,7 +1512,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>early September 2014</t>
+          <t>early-to-mid September 2014</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1556,12 +1542,12 @@
       <c r="O17" s="2" t="n"/>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>Deutsche Bank starts market-check outreach under #15; first replies 09/09, so outreach began 09/01–09/09. Filing’s total of six contacts = Parties A–F (A first seen #8; B–F #18–#21, #26). Ingredion continues diligence with standing bid #7.</t>
+          <t>Deutsche Bank market check: contacted six strategic counterparties to gauge interest while Ingredion continued diligence. First contacts reported 09/09 bound the start. Ingredion (live since #3) carried in; no bid due date set.</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>“Throughout early- to mid-September, in accordance with the board’s authorization, Deutsche Bank contacted six potential strategic counterparties in the same or similar industries to gauge initial interest” (p. 28)</t>
+          <t>Deutsche Bank contacted six potential strategic counterparties in the same or similar industries to gauge initial interest regarding a potential transaction with Penford (p. 28)</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
@@ -1622,12 +1608,12 @@
       <c r="O18" s="2" t="n"/>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Information given: Ingredion gets online data room access, plus diligence calls, meetings and site visits aimed at getting it to improve its terms.</t>
+          <t>Information access: Ingredion alone given online dataroom access, plus calls, meetings and site visits to encourage it to improve its terms. No dataroom or site visits reported for Parties A, C or D.</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>“Starting in early September, Penford provided Ingredion access to an online dataroom to review due diligence materials” (p. 27)</t>
+          <t>Starting in early September, Penford provided Ingredion access to an online dataroom to review due diligence materials (p. 28)</t>
         </is>
       </c>
       <c r="R18" s="2" t="n"/>
@@ -1648,12 +1634,12 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>09/09/2014</t>
+          <t>09/06/2014</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Party B</t>
+          <t>Ingredion</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1663,7 +1649,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F19" s="2" t="n">
@@ -1684,28 +1670,28 @@
       <c r="O19" s="2" t="n"/>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Deutsche Bank outreach; Party B expresses interest and is sent an NDA and standstill, but on 09/12 declines to proceed or sign. Never entered.</t>
+          <t>Ingredion (through J.P. Morgan) delivered its initial draft merger agreement, contemplating voting and support agreements by significant shareholders; standing offer then $18.00 (#7). No new price.</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>“Party B informed Deutsche Bank that it had decided not to move forward with discussions or sign a nondisclosure agreement” (p. 28)</t>
+          <t>J.P. Morgan Securities provided Deutsche Bank with an initial draft of a merger agreement (p. 28)</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="S19" s="2" t="n"/>
       <c r="T19" s="3" t="n">
-        <v>41891</v>
+        <v>41888</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>41891</v>
+        <v>41888</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>41891</v>
+        <v>41888</v>
       </c>
     </row>
     <row r="20">
@@ -1714,12 +1700,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>09/10/2014</t>
+          <t>09/09/2014</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Party C</t>
+          <t>Party A</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1750,28 +1736,28 @@
       <c r="O20" s="2" t="n"/>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Deutsche Bank outreach; Party C expresses interest in pursuing a transaction; NDA and standstill sent 09/11.</t>
+          <t>Deutsche Bank market-check contact (target-initiated); Party A expressed interest in further discussions and was sent an NDA and standstill. Party A had first approached Penford 08/01 (#8); listed here to reconcile the six contacted.</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>“a third potential strategic counterparty contacted by Deutsche Bank (referred to as Party C) expressed interest in pursuing a transaction” (p. 28)</t>
+          <t>On September 9, 2014, Party A expressed interest in having further discussions regarding a transaction (p. 28)</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="S20" s="2" t="n"/>
       <c r="T20" s="3" t="n">
-        <v>41892</v>
+        <v>41891</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>41892</v>
+        <v>41891</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>41892</v>
+        <v>41891</v>
       </c>
     </row>
     <row r="21">
@@ -1780,12 +1766,12 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>09/11/2014</t>
+          <t>09/09/2014</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Party D</t>
+          <t>Party B</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1816,28 +1802,28 @@
       <c r="O21" s="2" t="n"/>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Deutsche Bank outreach; Party D expresses interest and is sent an NDA and standstill.</t>
+          <t>Target-initiated (Deutsche Bank market check). Party B expressed interest and was sent an NDA and standstill; declined 09/12 (#23).</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>“a fourth potential strategic counterparty contacted by Deutsche Bank (referred to as Party D) expressed interest” (p. 28)</t>
+          <t>another strategic counterparty contacted by Deutsche Bank (referred to as Party B) expressed interest in further discussions (p. 28)</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="S21" s="2" t="n"/>
       <c r="T21" s="3" t="n">
-        <v>41893</v>
+        <v>41891</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>41893</v>
+        <v>41891</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>41893</v>
+        <v>41891</v>
       </c>
     </row>
     <row r="22">
@@ -1846,12 +1832,12 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>09/12/2014</t>
+          <t>09/10/2014</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Party E</t>
+          <t>Party C</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1882,28 +1868,28 @@
       <c r="O22" s="2" t="n"/>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>Deutsche Bank voicemail 09/12, then several more over two weeks; no response ever received. Never entered.</t>
+          <t>Target-initiated (Deutsche Bank market check). Party C expressed interest in pursuing a transaction; NDA and standstill forwarded 09/11/2014.</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>“Deutsche Bank also left several other voicemails for Party E regarding a potential transaction and received no response” (p. 28)</t>
+          <t>a third potential strategic counterparty contacted by Deutsche Bank (referred to as Party C) expressed interest in pursuing a transaction (p. 28)</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="S22" s="2" t="n"/>
       <c r="T22" s="3" t="n">
-        <v>41894</v>
+        <v>41892</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>41894</v>
+        <v>41892</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>41894</v>
+        <v>41892</v>
       </c>
     </row>
     <row r="23">
@@ -1912,12 +1898,12 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>09/15/2014</t>
+          <t>09/11/2014</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Party C</t>
+          <t>Party D</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1927,7 +1913,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>NDA signed</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="F23" s="2" t="n">
@@ -1948,24 +1934,28 @@
       <c r="O23" s="2" t="n"/>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>Entry. NDA and standstill; standstill lapses on announcement of a definitive sale agreement. Penford gives Party C information including financial projections the same day.</t>
+          <t>Target-initiated (Deutsche Bank market check). Party D expressed interest; NDA and standstill forwarded.</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>“Penford and Party C executed a nondisclosure and standstill agreement” (p. 28)</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="n"/>
+          <t>a fourth potential strategic counterparty contacted by Deutsche Bank (referred to as Party D) expressed interest (p. 28)</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
       <c r="S23" s="2" t="n"/>
       <c r="T23" s="3" t="n">
-        <v>41897</v>
+        <v>41893</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>41897</v>
+        <v>41893</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>41897</v>
+        <v>41893</v>
       </c>
     </row>
     <row r="24">
@@ -1974,12 +1964,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>09/17/2014</t>
+          <t>09/12/2014</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Ingredion</t>
+          <t>Party B</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1989,7 +1979,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
@@ -1998,27 +1988,11 @@
       <c r="G24" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H24" s="4" t="n">
-        <v>18.25</v>
-      </c>
-      <c r="I24" s="4" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
+      <c r="H24" s="2" t="n"/>
+      <c r="I24" s="2" t="n"/>
+      <c r="J24" s="2" t="n"/>
+      <c r="K24" s="2" t="n"/>
+      <c r="L24" s="2" t="n"/>
       <c r="M24" s="2" t="n">
         <v>1</v>
       </c>
@@ -2026,24 +2000,24 @@
       <c r="O24" s="2" t="n"/>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>Diligence open per narrative: facility visits being scheduled. Oral, after 09/16 Ingredion board: “could potentially increase” #7 to $18.25 or $18.50, fully diluted; revises cash proposal. Executive Committee disappointed (09/19, told 09/23). Ref: $14.70 close 09/16/2014; 24%/26% premium.</t>
+          <t>Declined: Party B told Deutsche Bank it would not move forward or sign an NDA. Never entered, so no exit row; one of the two parties that declined NDAs (10/14 report).</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>“Ingredion could potentially increase its proposal from $18.00 to $18.25 or $18.50 per share on a fully diluted basis” (p. 29)</t>
+          <t>Party B informed Deutsche Bank that it had decided not to move forward with discussions or sign a nondisclosure agreement (p. 28)</t>
         </is>
       </c>
       <c r="R24" s="2" t="n"/>
       <c r="S24" s="2" t="n"/>
       <c r="T24" s="3" t="n">
-        <v>41899</v>
+        <v>41894</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>41899</v>
+        <v>41894</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>41899</v>
+        <v>41894</v>
       </c>
     </row>
     <row r="25">
@@ -2052,12 +2026,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>09/23/2014</t>
+          <t>09/12/2014</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Party D</t>
+          <t>Party E</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -2067,7 +2041,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>NDA signed</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="F25" s="2" t="n">
@@ -2088,24 +2062,28 @@
       <c r="O25" s="2" t="n"/>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>Entry. NDA and standstill; standstill lapses on announcement of a definitive sale agreement. Strategic Plan projections went to all NDA signers (p. 43).</t>
+          <t>Target-initiated: Deutsche Bank voicemail; several more voicemails over the next two weeks drew no response. Never entered.</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>“Penford and Party D executed a nondisclosure and standstill agreement” (p. 29)</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="n"/>
+          <t>Deutsche Bank left a voicemail for another strategic counterparty (referred to as Party E) regarding a potential transaction (p. 28)</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
       <c r="S25" s="2" t="n"/>
       <c r="T25" s="3" t="n">
-        <v>41905</v>
+        <v>41894</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>41905</v>
+        <v>41894</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>41905</v>
+        <v>41894</v>
       </c>
     </row>
     <row r="26">
@@ -2114,18 +2092,22 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>09/24/2014</t>
+          <t>09/15/2014</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Penford</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="n"/>
+          <t>Party C</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>NDA signed</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
@@ -2139,29 +2121,31 @@
       <c r="J26" s="2" t="n"/>
       <c r="K26" s="2" t="n"/>
       <c r="L26" s="2" t="n"/>
-      <c r="M26" s="2" t="n"/>
+      <c r="M26" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N26" s="2" t="n"/>
       <c r="O26" s="2" t="n"/>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>Admission decision: board has Party F (one of the two largest industry players) approached but not Party G, citing confidentiality and misuse risks. Deutsche Bank reports weak interest among contacts. On 10/03 board again considered G and did not contact it.</t>
+          <t>NDA with standstill that falls away on announcement of a definitive sale agreement. Penford supplied information including strategy, segments, historical results and financial projections. Party C's entry.</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>“The board determined that Party F should be approached regarding a potential transaction with Penford, but due to the factors noted above, Party G should not be contacted.” (p. 29)</t>
+          <t>On September 15, 2014, Penford and Party C executed a nondisclosure and standstill agreement (p. 28)</t>
         </is>
       </c>
       <c r="R26" s="2" t="n"/>
       <c r="S26" s="2" t="n"/>
       <c r="T26" s="3" t="n">
-        <v>41906</v>
+        <v>41897</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>41906</v>
+        <v>41897</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>41906</v>
+        <v>41897</v>
       </c>
     </row>
     <row r="27">
@@ -2170,12 +2154,12 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>09/24/2014</t>
+          <t>09/17/2014</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Party F</t>
+          <t>Ingredion</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -2185,7 +2169,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F27" s="2" t="n">
@@ -2194,11 +2178,27 @@
       <c r="G27" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H27" s="2" t="n"/>
-      <c r="I27" s="2" t="n"/>
-      <c r="J27" s="2" t="n"/>
-      <c r="K27" s="2" t="n"/>
-      <c r="L27" s="2" t="n"/>
+      <c r="H27" s="4" t="n">
+        <v>18.25</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
       <c r="M27" s="2" t="n">
         <v>1</v>
       </c>
@@ -2206,28 +2206,28 @@
       <c r="O27" s="2" t="n"/>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>Deutsche Bank contacts Party F per #25; on 09/29 Party F says combination not a suitable strategic fit and declines further discussions. Never entered.</t>
+          <t>Unclear: diligence and facility visits still being scheduled; no condition stated. Oral, tentative: 'could potentially increase' from $18.00 to $18.25 or $18.50, fully diluted, after Ingredion board meeting 09/16. Ref: $14.70 close 09/16/2014; 24%/26% premium.</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>“Party F communicated to Deutsche Bank that a combination with Penford was not a suitable strategic fit and declined to pursue further discussions” (p. 30)</t>
+          <t>Ingredion could potentially increase its proposal from $18.00 to $18.25 or $18.50 per share on a fully diluted basis (p. 29)</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q2; Q4</t>
         </is>
       </c>
       <c r="S27" s="2" t="n"/>
       <c r="T27" s="3" t="n">
-        <v>41906</v>
+        <v>41899</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>41906</v>
+        <v>41899</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>41906</v>
+        <v>41899</v>
       </c>
     </row>
     <row r="28">
@@ -2236,12 +2236,12 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>09/25/2014</t>
+          <t>09/23/2014</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Party C</t>
+          <t>Party D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>NDA signed</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
@@ -2272,24 +2272,24 @@
       <c r="O28" s="2" t="n"/>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>Information given: in-person management presentation to Party C covering operations, strategy, financial performance and projections; Party A was later denied one unless competitive (#29).</t>
+          <t>NDA with standstill that falls away on announcement of a definitive sale agreement. Party D's entry; no information delivery reported.</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>“members of Penford’s management team provided a presentation to Party C” (p. 29)</t>
+          <t>On September 23, 2014, Penford and Party D executed a nondisclosure and standstill agreement (p. 29)</t>
         </is>
       </c>
       <c r="R28" s="2" t="n"/>
       <c r="S28" s="2" t="n"/>
       <c r="T28" s="3" t="n">
-        <v>41907</v>
+        <v>41905</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>41907</v>
+        <v>41905</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>41907</v>
+        <v>41905</v>
       </c>
     </row>
     <row r="29">
@@ -2298,22 +2298,18 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>09/30/2014</t>
+          <t>09/24/2014</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Party A</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Penford</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n"/>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>NDA signed</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F29" s="2" t="n">
@@ -2327,35 +2323,29 @@
       <c r="J29" s="2" t="n"/>
       <c r="K29" s="2" t="n"/>
       <c r="L29" s="2" t="n"/>
-      <c r="M29" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M29" s="2" t="n"/>
       <c r="N29" s="2" t="n"/>
       <c r="O29" s="2" t="n"/>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>Entry. NDA and standstill (lapses on announcement of a definitive sale agreement); Deutsche Bank gives information including financial projections. Party A re-expressed interest to Deutsche Bank 09/09 and is counted among its six contacts.</t>
+          <t>Admission decision: board had Deutsche Bank approach Party F but not Party G (the two largest industry companies), citing interest, timing and confidentiality/misuse risk. Deutsche Bank reported market interest 'not particularly strong'. Party G reconsidered 10/03, not contacted.</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>“Penford and Party A executed a nondisclosure and standstill agreement” (p. 30)</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
+          <t>The board determined that Party F should be approached regarding a potential transaction with Penford, but due to the factors noted above, Party G should not be contacted. (p. 29)</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="n"/>
       <c r="S29" s="2" t="n"/>
       <c r="T29" s="3" t="n">
-        <v>41912</v>
+        <v>41906</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>41912</v>
+        <v>41906</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>41912</v>
+        <v>41906</v>
       </c>
     </row>
     <row r="30">
@@ -2364,12 +2354,12 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>09/30/2014</t>
+          <t>09/24/2014</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Party A</t>
+          <t>Party F</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -2379,7 +2369,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
@@ -2400,24 +2390,28 @@
       <c r="O30" s="2" t="n"/>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>Access withheld and price requirement: Deutsche Bank tells Party A no in-person management presentation unless its price is competitive, likely meaning over $20.00 per share.</t>
+          <t>Target-initiated: Deutsche Bank contacted Party F, one of the two largest companies in Penford's industry, on the board's authorization.</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>“Penford would not provide in-person management presentations unless there was an indication that Party A’s proposed offer price would be competitive” (p. 30)</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="n"/>
+          <t>On September 24, 2014, in accordance with the board’s authorization, Deutsche Bank contacted Party F regarding a potential transaction with Penford. (p. 29)</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
       <c r="S30" s="2" t="n"/>
       <c r="T30" s="3" t="n">
-        <v>41912</v>
+        <v>41906</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>41912</v>
+        <v>41906</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>41912</v>
+        <v>41906</v>
       </c>
     </row>
     <row r="31">
@@ -2426,15 +2420,19 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>10/01/2014</t>
+          <t>09/25/2014</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Penford</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="n"/>
+          <t>Party C</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Other material event</t>
@@ -2451,29 +2449,31 @@
       <c r="J31" s="2" t="n"/>
       <c r="K31" s="2" t="n"/>
       <c r="L31" s="2" t="n"/>
-      <c r="M31" s="2" t="n"/>
+      <c r="M31" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N31" s="2" t="n"/>
       <c r="O31" s="2" t="n"/>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>Price requirement: Deutsche Bank tells J.P. Morgan the board is disappointed with $18.25–$18.50 (#23) and wanted at least $20.00. On 09/29 board had said it wanted $0.50–$1.00 more. On 10/02 Malkoski said Penford would still negotiate.</t>
+          <t>Information access: in-person management presentation to Party C (operations, strategy, financial performance and projections). Party A was later refused one unless its price was competitive (#34); none reported for Party D.</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>“Deutsche Bank further explained that Penford’s board of directors had wanted a purchase price of at least $20.00 per share.” (p. 30)</t>
+          <t>members of Penford’s management team provided a presentation to Party C (p. 29)</t>
         </is>
       </c>
       <c r="R31" s="2" t="n"/>
       <c r="S31" s="2" t="n"/>
       <c r="T31" s="3" t="n">
-        <v>41913</v>
+        <v>41907</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>41913</v>
+        <v>41907</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>41913</v>
+        <v>41907</v>
       </c>
     </row>
     <row r="32">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>10/02/2014</t>
+          <t>09/29/2014</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Ingredion</t>
+          <t>Party F</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F32" s="2" t="n">
@@ -2506,27 +2506,11 @@
       <c r="G32" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H32" s="4" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="I32" s="4" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
+      <c r="H32" s="2" t="n"/>
+      <c r="I32" s="2" t="n"/>
+      <c r="J32" s="2" t="n"/>
+      <c r="K32" s="2" t="n"/>
+      <c r="L32" s="2" t="n"/>
       <c r="M32" s="2" t="n">
         <v>1</v>
       </c>
@@ -2534,24 +2518,24 @@
       <c r="O32" s="2" t="n"/>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>Diligence open per narrative: Penford offering more information and meetings to support a higher price. Oral on call: Ingredion prepared to move forward at $18.50 fully diluted, top of #23; revises cash proposal. Malkoski: unlikely to win recommendation.</t>
+          <t>Declined: Party F said a combination was not a suitable strategic fit and declined further discussions. Never signed an NDA, so no exit row.</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>“Mr. Fortnum then stated that Ingredion was prepared to move forward based on a proposed price of $18.50 per share on a fully diluted basis.” (p. 30)</t>
+          <t>Party F communicated to Deutsche Bank that a combination with Penford was not a suitable strategic fit and declined to pursue further discussions (p. 30)</t>
         </is>
       </c>
       <c r="R32" s="2" t="n"/>
       <c r="S32" s="2" t="n"/>
       <c r="T32" s="3" t="n">
-        <v>41914</v>
+        <v>41911</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>41914</v>
+        <v>41911</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>41914</v>
+        <v>41911</v>
       </c>
     </row>
     <row r="33">
@@ -2560,22 +2544,18 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>10/02/2014</t>
+          <t>09/29/2014</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Ingredion</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Penford</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n"/>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F33" s="2" t="n">
@@ -2584,56 +2564,34 @@
       <c r="G33" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H33" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="I33" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="H33" s="2" t="n"/>
+      <c r="I33" s="2" t="n"/>
+      <c r="J33" s="2" t="n"/>
+      <c r="K33" s="2" t="n"/>
+      <c r="L33" s="2" t="n"/>
+      <c r="M33" s="2" t="n"/>
       <c r="N33" s="2" t="n"/>
       <c r="O33" s="2" t="n"/>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>Diligence open per narrative: same-day call contemplated more information and meetings (#31). Letter, a “revised indication of interest”, fully diluted; cash inferred as revision of cash indication #7. Ref: $12.77 close 10/01/2014; 49% premium.</t>
+          <t>Price requirement (internal): board wanted Ingredion's $18.25–$18.50 raised a further $0.50–$1.00 and approved further negotiation. Executive Committee disappointment (09/19) had been relayed to Ingredion 09/23.</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>“increasing the proposed price to $19.00 per share of outstanding Penford capital stock on a fully diluted basis” (p. 30)</t>
-        </is>
-      </c>
-      <c r="R33" s="2" t="inlineStr">
-        <is>
-          <t>Q4</t>
-        </is>
-      </c>
+          <t>the board indicated it would prefer to see the per share price increase by an additional $0.50 to $1.00 (p. 30)</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="n"/>
       <c r="S33" s="2" t="n"/>
       <c r="T33" s="3" t="n">
-        <v>41914</v>
+        <v>41911</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>41914</v>
+        <v>41911</v>
       </c>
       <c r="V33" s="3" t="n">
-        <v>41914</v>
+        <v>41911</v>
       </c>
     </row>
     <row r="34">
@@ -2642,18 +2600,22 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>10/03/2014</t>
+          <t>09/30/2014</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Penford</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="n"/>
+          <t>Party A</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>NDA signed</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
@@ -2667,33 +2629,31 @@
       <c r="J34" s="2" t="n"/>
       <c r="K34" s="2" t="n"/>
       <c r="L34" s="2" t="n"/>
-      <c r="M34" s="2" t="n"/>
+      <c r="M34" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N34" s="2" t="n"/>
       <c r="O34" s="2" t="n"/>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>Preferred bidder: board directs management to negotiate and finalize a definitive agreement with Ingredion at $19.00 (#32). Deutsche Bank: Party A unlikely to reach $20.00; no other contact will propose. Party G again not contacted. No exclusivity granted.</t>
+          <t>NDA with standstill that falls away on announcement of a definitive sale agreement; Deutsche Bank sent information including historical results and financial projections. Party A's entry.</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>“the directors present at the board meeting unanimously directed management to proceed to negotiate and finalize a definitive agreement with Ingredion” (p. 31)</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>Q3; Q4</t>
-        </is>
-      </c>
+          <t>On September 30, 2014, Penford and Party A executed a nondisclosure and standstill agreement (p. 30)</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="n"/>
       <c r="S34" s="2" t="n"/>
       <c r="T34" s="3" t="n">
-        <v>41915</v>
+        <v>41912</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>41915</v>
+        <v>41912</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>41915</v>
+        <v>41912</v>
       </c>
     </row>
     <row r="35">
@@ -2702,58 +2662,60 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>10/03/2014</t>
+          <t>09/30/2014</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Penford</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="n"/>
+          <t>Party A</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Round opened</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F35" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H35" s="2" t="n"/>
       <c r="I35" s="2" t="n"/>
       <c r="J35" s="2" t="n"/>
       <c r="K35" s="2" t="n"/>
       <c r="L35" s="2" t="n"/>
-      <c r="M35" s="2" t="n"/>
+      <c r="M35" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N35" s="2" t="n"/>
       <c r="O35" s="2" t="n"/>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>Definitive negotiation with Ingredion alone follows #33: Malkoski tells Fortnum; Perkins Coie sends revised draft merger agreement to Sidley Austin. Parties A, C and D stay under NDA in the continuing market check, not admitted to this stage.</t>
+          <t>Information access and price requirement: Deutsche Bank told Party A there would be no in-person management presentation unless its price looked competitive, likely over $20.00 per share (contrast Party C, #30; Ingredion, #13).</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>“Mr. Malkoski informed Mr. Fortnum that the Penford board had authorized management to move forward with negotiating the draft merger agreement” (p. 31)</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>Q3</t>
-        </is>
-      </c>
+          <t>Penford would not provide in-person management presentations unless there was an indication that Party A’s proposed offer price would be competitive (p. 30)</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="n"/>
       <c r="S35" s="2" t="n"/>
       <c r="T35" s="3" t="n">
-        <v>41915</v>
+        <v>41912</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>41915</v>
+        <v>41912</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>41915</v>
+        <v>41912</v>
       </c>
     </row>
     <row r="36">
@@ -2762,25 +2724,25 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>10/03/2014</t>
+          <t>10/01/2014</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Sidley Austin LLP</t>
+          <t>Penford</t>
         </is>
       </c>
       <c r="D36" s="2" t="n"/>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Adviser</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H36" s="2" t="n"/>
       <c r="I36" s="2" t="n"/>
@@ -2792,24 +2754,24 @@
       <c r="O36" s="2" t="n"/>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>Ingredion’s legal counsel; first seen acting 10/03, receiving Penford’s revised draft merger agreement.</t>
+          <t>Price requirement: Deutsche Bank told J.P. Morgan the board was disappointed with $18.25–$18.50 and wanted at least $20.00 per share. On 10/02 Malkoski said the board wanted about $20.00 but would keep negotiating.</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>“Perkins Coie sent a revised draft of the merger agreement to Sidley Austin LLP (referred to as Sidley Austin), Ingredion’s legal counsel” (p. 31)</t>
+          <t>Deutsche Bank further explained that Penford’s board of directors had wanted a purchase price of at least $20.00 per share. (p. 30)</t>
         </is>
       </c>
       <c r="R36" s="2" t="n"/>
       <c r="S36" s="2" t="n"/>
       <c r="T36" s="3" t="n">
-        <v>41915</v>
+        <v>41913</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>41915</v>
+        <v>41913</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>41915</v>
+        <v>41913</v>
       </c>
     </row>
     <row r="37">
@@ -2818,12 +2780,12 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>10/04/2014</t>
+          <t>10/02/2014</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Party A</t>
+          <t>Ingredion</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2833,7 +2795,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F37" s="2" t="n">
@@ -2842,11 +2804,27 @@
       <c r="G37" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H37" s="2" t="n"/>
-      <c r="I37" s="2" t="n"/>
-      <c r="J37" s="2" t="n"/>
-      <c r="K37" s="2" t="n"/>
-      <c r="L37" s="2" t="n"/>
+      <c r="H37" s="4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="I37" s="4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
       <c r="M37" s="2" t="n">
         <v>1</v>
       </c>
@@ -2854,28 +2832,28 @@
       <c r="O37" s="2" t="n"/>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>Valuation statement without an offer: on Deutsche Bank follow-up, Party A says any offer would be below $17.50–$18.00 per share in cash; Deutsche Bank urges a letter of interest for the board.</t>
+          <t>Unclear: no condition stated; diligence meetings still continuing. Oral: Fortnum said Ingredion was prepared to move forward at $18.50 fully diluted, narrowing #26's range; Malkoski said unlikely to win a board recommendation.</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>“Party A indicated any offer would be below $17.50 - $18.00 per share in cash” (p. 31)</t>
+          <t>Mr. Fortnum then stated that Ingredion was prepared to move forward based on a proposed price of $18.50 per share on a fully diluted basis. (p. 30)</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>Q5</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="S37" s="2" t="n"/>
       <c r="T37" s="3" t="n">
-        <v>41916</v>
+        <v>41914</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>41916</v>
+        <v>41914</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>41916</v>
+        <v>41914</v>
       </c>
     </row>
     <row r="38">
@@ -2884,54 +2862,80 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>10/07/2014</t>
+          <t>10/02/2014</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Milbank, Tweed, Hadley &amp; McCloy LLP</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="n"/>
+          <t>Ingredion</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Adviser</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H38" s="2" t="n"/>
-      <c r="I38" s="2" t="n"/>
-      <c r="J38" s="2" t="n"/>
-      <c r="K38" s="2" t="n"/>
-      <c r="L38" s="2" t="n"/>
-      <c r="M38" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N38" s="2" t="n"/>
       <c r="O38" s="2" t="n"/>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>SEACOR’s legal counsel; first seen acting 10/07 when contacted by Perkins Coie about the voting agreement; negotiated it with Sidley Austin through 10/14.</t>
+          <t>Unclear: no condition stated; year-end financials not yet delivered (#44). Letter, later same day, revising the indication of interest to $19.00 fully diluted; cash not stated. Ref: $12.77 close 10/01/2014; 49% premium.</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>“Milbank, Tweed, Hadley &amp; McCloy, LLP (referred to as Milbank), legal counsel to SEACOR” (p. 31)</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="n"/>
+          <t>Penford received a letter from Ingredion regarding its indication of interest and increasing the proposed price to $19.00 per share (p. 30)</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
       <c r="S38" s="2" t="n"/>
       <c r="T38" s="3" t="n">
-        <v>41919</v>
+        <v>41914</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>41919</v>
+        <v>41914</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>41919</v>
+        <v>41914</v>
       </c>
     </row>
     <row r="39">
@@ -2940,18 +2944,18 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>10/07/2014</t>
+          <t>10/03/2014</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>SEACOR</t>
+          <t>Penford</t>
         </is>
       </c>
       <c r="D39" s="2" t="n"/>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Round opened</t>
         </is>
       </c>
       <c r="F39" s="2" t="n">
@@ -2970,24 +2974,28 @@
       <c r="O39" s="2" t="n"/>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>Support relationship formed in principle: Ingredion requires SEACOR voting and support agreement (in its 09/06 draft); Milbank says acceptable if it ends when the merger agreement is terminated for a superior offer. Executed at signing (#45).</t>
+          <t>Board directed management to negotiate and finalize a definitive agreement with Ingredion after Deutsche Bank said Party A was unlikely to reach $20.00 and no other contact would propose. Ingredion told same day; merger agreement drafts exchanged from 10/03.</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>“Milbank indicated that conceptually, a voting and support agreement to support the transaction would be acceptable, subject to discussions with SEACOR” (p. 31)</t>
-        </is>
-      </c>
-      <c r="R39" s="2" t="n"/>
+          <t>the directors present at the board meeting unanimously directed management to proceed to negotiate and finalize a definitive agreement with Ingredion (p. 31)</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
       <c r="S39" s="2" t="n"/>
       <c r="T39" s="3" t="n">
-        <v>41919</v>
+        <v>41915</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>41919</v>
+        <v>41915</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>41919</v>
+        <v>41915</v>
       </c>
     </row>
     <row r="40">
@@ -2996,22 +3004,18 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>10/08/2014</t>
+          <t>10/03/2014</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Ingredion</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Sidley Austin LLP</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n"/>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Bid reaffirmed</t>
+          <t>Adviser</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
@@ -3020,56 +3024,34 @@
       <c r="G40" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H40" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="I40" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="H40" s="2" t="n"/>
+      <c r="I40" s="2" t="n"/>
+      <c r="J40" s="2" t="n"/>
+      <c r="K40" s="2" t="n"/>
+      <c r="L40" s="2" t="n"/>
+      <c r="M40" s="2" t="n"/>
       <c r="N40" s="2" t="n"/>
       <c r="O40" s="2" t="n"/>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>Final documentation outstanding: open points included delivery of FY2014 financial statements as closing condition, antitrust divestiture scope, termination fee. Reaffirmed by returned draft: Sidley Austin returns revised merger agreement after Penford’s 10/03 draft; $19.00 carried from #32.</t>
+          <t>Ingredion's legal counsel; earliest shown acting 10/03/2014, receiving Perkins Coie's revised draft merger agreement.</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>“On October 8, 2014, Sidley Austin circulated a revised draft of the merger agreement to Perkins Coie.” (p. 31)</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>Q4</t>
-        </is>
-      </c>
+          <t>Perkins Coie sent a revised draft of the merger agreement to Sidley Austin LLP (referred to as Sidley Austin), Ingredion’s legal counsel (p. 31)</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="n"/>
       <c r="S40" s="2" t="n"/>
       <c r="T40" s="3" t="n">
-        <v>41920</v>
+        <v>41915</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>41920</v>
+        <v>41915</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>41920</v>
+        <v>41915</v>
       </c>
     </row>
     <row r="41">
@@ -3078,12 +3060,12 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>10/08/2014</t>
+          <t>10/04/2014</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Party D</t>
+          <t>Party A</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -3093,14 +3075,14 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Withdrew</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F41" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H41" s="2" t="n"/>
       <c r="I41" s="2" t="n"/>
@@ -3110,32 +3092,32 @@
       <c r="M41" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
+      <c r="N41" s="2" t="n"/>
       <c r="O41" s="2" t="n"/>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>At meeting with Deutsche Bank, Party D says it will not move forward; no reason given. Bidder’s decision.</t>
+          <t>Valuation statement without offer: on Deutsche Bank follow-up, Party A said any offer would be below $17.50–$18.00 per share in cash; Deutsche Bank encouraged a letter of interest for the board. Party A not admitted to round 2.</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>“Party D, who indicated that it did not intend to move forward with discussions regarding a potential transaction involving the Company” (p. 31)</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="n"/>
+          <t>Party A indicated any offer would be below $17.50 - $18.00 per share in cash (p. 31)</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
       <c r="S41" s="2" t="n"/>
       <c r="T41" s="3" t="n">
-        <v>41920</v>
+        <v>41916</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>41920</v>
+        <v>41916</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>41920</v>
+        <v>41916</v>
       </c>
     </row>
     <row r="42">
@@ -3144,22 +3126,18 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>10/11/2014</t>
+          <t>10/07/2014</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Ingredion</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Milbank, Tweed, Hadley &amp; McCloy, LLP</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n"/>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Adviser</t>
         </is>
       </c>
       <c r="F42" s="2" t="n">
@@ -3173,31 +3151,29 @@
       <c r="J42" s="2" t="n"/>
       <c r="K42" s="2" t="n"/>
       <c r="L42" s="2" t="n"/>
-      <c r="M42" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M42" s="2" t="n"/>
       <c r="N42" s="2" t="n"/>
       <c r="O42" s="2" t="n"/>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>Information given: draft FY2014 financial statements, showing lower volume, revenue and EBITDA than the projections given earlier; accounting calls 10/11–10/12. On 10/13 Fortnum says figures might hurt Ingredion’s valuation. Adjusted Strategic Plan went only to Deutsche Bank, 10/10 (p. 43).</t>
+          <t>SEACOR's legal counsel; earliest shown acting 10/07/2014 when Perkins Coie raised Ingredion's request for a SEACOR voting and support agreement, which Milbank said was conceptually acceptable if it ended on termination for a superior offer.</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>“Penford provided Ingredion with draft financial statements for the fiscal year ended August 31, 2014” (p. 31)</t>
+          <t>Milbank, Tweed, Hadley &amp; McCloy, LLP (referred to as Milbank), legal counsel to SEACOR (p. 31)</t>
         </is>
       </c>
       <c r="R42" s="2" t="n"/>
       <c r="S42" s="2" t="n"/>
       <c r="T42" s="3" t="n">
-        <v>41923</v>
+        <v>41919</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>41923</v>
+        <v>41919</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>41923</v>
+        <v>41919</v>
       </c>
     </row>
     <row r="43">
@@ -3206,12 +3182,12 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>10/13/2014</t>
+          <t>10/08/2014</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Party A</t>
+          <t>Party D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -3221,7 +3197,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Withdrew</t>
         </is>
       </c>
       <c r="F43" s="2" t="n">
@@ -3238,32 +3214,32 @@
       <c r="M43" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N43" s="2" t="n"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
       <c r="O43" s="2" t="n"/>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>Valuation statement without an offer: Party A tells Deutsche Bank its value range fell from $17.50–$18.00 to $16.00–$18.00 per share, citing market volatility.</t>
+          <t>Party D told Deutsche Bank at a meeting that it did not intend to move forward with discussions. No bid; no reason given. Round 1 is the round being left (not admitted to round 2).</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t>“its value range for a potential transaction had been reduced from $17.50 - $18.00 per share to $16.00 - $18.00 per share” (p. 32)</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>Q5</t>
-        </is>
-      </c>
+          <t>Party D, who indicated that it did not intend to move forward with discussions regarding a potential transaction involving the Company (p. 31)</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="n"/>
       <c r="S43" s="2" t="n"/>
       <c r="T43" s="3" t="n">
-        <v>41925</v>
+        <v>41920</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>41925</v>
+        <v>41920</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>41925</v>
+        <v>41920</v>
       </c>
     </row>
     <row r="44">
@@ -3272,22 +3248,18 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>10/14/2014</t>
+          <t>10/10/2014</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Ingredion</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Penford</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n"/>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Bid reaffirmed</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
@@ -3296,56 +3268,34 @@
       <c r="G44" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H44" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="I44" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="H44" s="2" t="n"/>
+      <c r="I44" s="2" t="n"/>
+      <c r="J44" s="2" t="n"/>
+      <c r="K44" s="2" t="n"/>
+      <c r="L44" s="2" t="n"/>
+      <c r="M44" s="2" t="n"/>
       <c r="N44" s="2" t="n"/>
       <c r="O44" s="2" t="n"/>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>Ready to sign: wants to enter merger agreement promptly (p. 32); no financing condition, funds from cash and revolver (p. 45). Reaffirmed by price confirmation: $19.00 carried from #32 despite weaker FY2014 figures (#41).</t>
+          <t>Projections revised after bidding began: Adjusted Strategic Plan, pushing growth targets out one year, provided to Deutsche Bank and used for its opinion. From projections section; filing does not say bidders received it.</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>“Mr. Fortnum called Mr. Malkoski to confirm the proposed price of $19.00 and discuss finalizing the draft merger agreement” (p. 32)</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t>Q4</t>
-        </is>
-      </c>
+          <t>The Adjusted Strategic Plan was provided to Deutsche Bank on October 10, 2014. (p. 43)</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="n"/>
       <c r="S44" s="2" t="n"/>
       <c r="T44" s="3" t="n">
-        <v>41926</v>
+        <v>41922</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>41926</v>
+        <v>41922</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>41926</v>
+        <v>41922</v>
       </c>
     </row>
     <row r="45">
@@ -3354,12 +3304,12 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>10/14/2014</t>
+          <t>10/11/2014</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Party A</t>
+          <t>Ingredion</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -3369,36 +3319,20 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F45" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H45" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="I45" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H45" s="2" t="n"/>
+      <c r="I45" s="2" t="n"/>
+      <c r="J45" s="2" t="n"/>
+      <c r="K45" s="2" t="n"/>
+      <c r="L45" s="2" t="n"/>
       <c r="M45" s="2" t="n">
         <v>1</v>
       </c>
@@ -3406,28 +3340,24 @@
       <c r="O45" s="2" t="n"/>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>Diligence open per narrative: no management presentation given (#29). Letter of indication of interest answering Deutsche Bank’s 10/04 request (#36); cut from earlier range, citing market volatility. Form of consideration not stated in letter. Ref: $11.07 close 10/13/2014; 45% premium.</t>
+          <t>Information access: Penford gave Ingredion draft FY2014 financial statements showing lower volume, revenue and EBITDA than the strategic-plan projections; 10/13 Fortnum said this might hurt Ingredion's valuation. Not reported as given to Party A.</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>“Party A provided a formal letter with its indication of interest with respect to an acquisition of the Company at a price of $16.00 per share” (p. 32)</t>
-        </is>
-      </c>
-      <c r="R45" s="2" t="inlineStr">
-        <is>
-          <t>Q3; Q5</t>
-        </is>
-      </c>
+          <t>On October 11, 2014, Penford provided Ingredion with draft financial statements for the fiscal year ended August 31, 2014 (p. 31)</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="n"/>
       <c r="S45" s="2" t="n"/>
       <c r="T45" s="3" t="n">
-        <v>41926</v>
+        <v>41923</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>41926</v>
+        <v>41923</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>41926</v>
+        <v>41923</v>
       </c>
     </row>
     <row r="46">
@@ -3436,12 +3366,12 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>10/14/2014</t>
+          <t>10/13/2014</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Ingredion</t>
+          <t>Party A</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -3451,7 +3381,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Merger agreement signed</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F46" s="2" t="n">
@@ -3472,24 +3402,28 @@
       <c r="O46" s="2" t="n"/>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>$19.00 per share in cash, via merger with Prospect Sub, Inc. Signed the evening after board approval and Deutsche Bank fairness opinion; Penford, Ingredion and SEACOR also sign the voting and support agreement (#38).</t>
+          <t>Valuation statement without offer: Party A told Deutsche Bank its value range fell from $17.50–$18.00 to $16.00–$18.00 per share, citing market volatility.</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>“During the evening on October 14, 2014, Penford and Ingredion finalized and executed the merger agreement” (p. 33)</t>
-        </is>
-      </c>
-      <c r="R46" s="2" t="n"/>
+          <t>its value range for a potential transaction had been reduced from $17.50 - $18.00 per share to $16.00 - $18.00 per share (p. 32)</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
       <c r="S46" s="2" t="n"/>
       <c r="T46" s="3" t="n">
-        <v>41926</v>
+        <v>41925</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>41926</v>
+        <v>41925</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>41926</v>
+        <v>41925</v>
       </c>
     </row>
     <row r="47">
@@ -3503,7 +3437,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Party A</t>
+          <t>Ingredion</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -3513,42 +3447,54 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Not selected at signing</t>
+          <t>Bid reaffirmed</t>
         </is>
       </c>
       <c r="F47" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H47" s="2" t="n"/>
-      <c r="I47" s="2" t="n"/>
-      <c r="J47" s="2" t="n"/>
-      <c r="K47" s="2" t="n"/>
-      <c r="L47" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="H47" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="I47" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="M47" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N47" s="2" t="inlineStr">
-        <is>
-          <t>Lower offer than rivals</t>
-        </is>
-      </c>
+      <c r="N47" s="2" t="n"/>
       <c r="O47" s="2" t="n"/>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>Party A’s $16.00 (#44) was below Ingredion’s $19.00; Deutsche Bank told the board the three remaining NDA signers did not move forward in time or made a lower indication. Target’s decision.</t>
+          <t>None: ready to sign; no financing condition (cash and revolver), diligence complete. Fortnum confirmed $19.00 (carried from #37) despite weaker draft financials and asked to finalize the agreement. Agreement adds a year-end financials closing condition.</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
         <is>
-          <t>“the remaining three of which either did not move forward in a timely manner or made a lower indication of value” (p. 32)</t>
+          <t>Mr. Fortnum called Mr. Malkoski to confirm the proposed price of $19.00 and discuss finalizing the draft merger agreement (p. 32)</t>
         </is>
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>Q5</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="S47" s="2" t="n"/>
@@ -3568,12 +3514,12 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>by 10/14/2014</t>
+          <t>10/14/2014</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Party C</t>
+          <t>Party A</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -3583,46 +3529,54 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Not selected at signing</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F48" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H48" s="2" t="n"/>
-      <c r="I48" s="2" t="n"/>
-      <c r="J48" s="2" t="n"/>
-      <c r="K48" s="2" t="n"/>
-      <c r="L48" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="H48" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="I48" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
       <c r="M48" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N48" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="O48" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="N48" s="2" t="n"/>
+      <c r="O48" s="2" t="n"/>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>Inferred: last seen at the 09/25 management presentation, no reported exit. Of the three remaining NDA signers, D withdrew (#40) and A bid lower (#44), so C is the one that “did not move forward in a timely manner”.</t>
+          <t>Unclear: no conditions reported; Party A never had a management presentation. Formal letter of interest at $16.00, lowered for market volatility; cash not stated. Received, not admitted to round 2. Ref: $11.07 close 10/13/2014; 45% premium.</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>“the remaining three of which either did not move forward in a timely manner or made a lower indication of value” (p. 32)</t>
+          <t>Party A provided a formal letter with its indication of interest with respect to an acquisition of the Company at a price of $16.00 per share (p. 32)</t>
         </is>
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>Q6</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="S48" s="2" t="n"/>
@@ -3630,7 +3584,7 @@
         <v>41926</v>
       </c>
       <c r="U48" s="3" t="n">
-        <v>41907</v>
+        <v>41926</v>
       </c>
       <c r="V48" s="3" t="n">
         <v>41926</v>
@@ -3642,60 +3596,318 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>10/15/2014</t>
+          <t>10/14/2014</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Penford</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="n"/>
+          <t>Ingredion</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Merger announced</t>
+          <t>Merger agreement signed</t>
         </is>
       </c>
       <c r="F49" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
+      <c r="G49" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="H49" s="2" t="n"/>
       <c r="I49" s="2" t="n"/>
       <c r="J49" s="2" t="n"/>
       <c r="K49" s="2" t="n"/>
       <c r="L49" s="2" t="n"/>
-      <c r="M49" s="2" t="n"/>
+      <c r="M49" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N49" s="2" t="n"/>
       <c r="O49" s="2" t="n"/>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>Penford and Ingredion issue press releases before market open.</t>
+          <t>Signed evening of 10/14/2014 after unanimous board approval and Deutsche Bank's fairness opinion: $19.00 per share in cash through Prospect Sub, Inc.; no financing condition; $7.6 million termination fee.</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
         <is>
-          <t>“Penford and Ingredion issued press releases announcing the transaction on October 15, 2014 prior to the opening of trading” (p. 33)</t>
+          <t>During the evening on October 14, 2014, Penford and Ingredion finalized and executed the merger agreement (p. 33)</t>
         </is>
       </c>
       <c r="R49" s="2" t="n"/>
       <c r="S49" s="2" t="n"/>
       <c r="T49" s="3" t="n">
+        <v>41926</v>
+      </c>
+      <c r="U49" s="3" t="n">
+        <v>41926</v>
+      </c>
+      <c r="V49" s="3" t="n">
+        <v>41926</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>10/14/2014</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>SEACOR</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n"/>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Other material event</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H50" s="2" t="n"/>
+      <c r="I50" s="2" t="n"/>
+      <c r="J50" s="2" t="n"/>
+      <c r="K50" s="2" t="n"/>
+      <c r="L50" s="2" t="n"/>
+      <c r="M50" s="2" t="n"/>
+      <c r="N50" s="2" t="n"/>
+      <c r="O50" s="2" t="n"/>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>Voting support: SEACOR (about 9.28%) signed a voting and support agreement with Ingredion and Penford to vote for the merger and not solicit proxies for its nominees until termination, adverse amendment or 03/15/2015.</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>Penford, Ingredion and SEACOR executed the voting and support agreement (p. 33)</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="n"/>
+      <c r="S50" s="2" t="n"/>
+      <c r="T50" s="3" t="n">
+        <v>41926</v>
+      </c>
+      <c r="U50" s="3" t="n">
+        <v>41926</v>
+      </c>
+      <c r="V50" s="3" t="n">
+        <v>41926</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>10/14/2014</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Party A</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Not selected at signing</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H51" s="2" t="n"/>
+      <c r="I51" s="2" t="n"/>
+      <c r="J51" s="2" t="n"/>
+      <c r="K51" s="2" t="n"/>
+      <c r="L51" s="2" t="n"/>
+      <c r="M51" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>Lower offer than rivals</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="n"/>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>Still live when Penford signed with Ingredion at $19.00; its $16.00 letter (#47) was lower. Deutsche Bank's 10/14 report grouped A, C, D as not moving forward in time or giving a lower value.</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>the remaining three of which either did not move forward in a timely manner or made a lower indication of value (p. 32)</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
+      </c>
+      <c r="S51" s="2" t="n"/>
+      <c r="T51" s="3" t="n">
+        <v>41926</v>
+      </c>
+      <c r="U51" s="3" t="n">
+        <v>41926</v>
+      </c>
+      <c r="V51" s="3" t="n">
+        <v>41926</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>by 10/14/2014</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Party C</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Not selected at signing</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" s="2" t="n"/>
+      <c r="I52" s="2" t="n"/>
+      <c r="J52" s="2" t="n"/>
+      <c r="K52" s="2" t="n"/>
+      <c r="L52" s="2" t="n"/>
+      <c r="M52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>Inferred: last reported at its 09/25 presentation, under NDA; no proposal (per 10/03 report) and no exit reported. Deutsche Bank's 10/14 summary places it among parties that did not move forward in a timely manner or bid lower.</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>no other companies that had been contacted during the market check process indicated they would provide a proposal or other indication of interest (p. 30)</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
+      </c>
+      <c r="S52" s="2" t="n"/>
+      <c r="T52" s="3" t="n">
+        <v>41926</v>
+      </c>
+      <c r="U52" s="2" t="n"/>
+      <c r="V52" s="2" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>10/15/2014</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Penford</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n"/>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Merger announced</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="n"/>
+      <c r="I53" s="2" t="n"/>
+      <c r="J53" s="2" t="n"/>
+      <c r="K53" s="2" t="n"/>
+      <c r="L53" s="2" t="n"/>
+      <c r="M53" s="2" t="n"/>
+      <c r="N53" s="2" t="n"/>
+      <c r="O53" s="2" t="n"/>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>Penford and Ingredion issued press releases before market open.</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>Penford and Ingredion issued press releases announcing the transaction on October 15, 2014 prior to the opening of trading. (p. 33)</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="n"/>
+      <c r="S53" s="2" t="n"/>
+      <c r="T53" s="3" t="n">
         <v>41927</v>
       </c>
-      <c r="U49" s="3" t="n">
+      <c r="U53" s="3" t="n">
         <v>41927</v>
       </c>
-      <c r="V49" s="3" t="n">
+      <c r="V53" s="3" t="n">
         <v>41927</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V49"/>
+  <autoFilter ref="A1:V53"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3785,12 +3997,12 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Deutsche Bank began market-check outreach to strategic counterparties (early September) under the 08/28 board authorization, while Ingredion continued diligence (#16)</t>
+          <t>Deutsche Bank market-check outreach to six strategic counterparties, early-to-mid September 2014 (first contacts reported 09/09), carrying out the board’s 08/28 authorization (#16).</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>4 strategic: Ingredion (under NDA since round 0; standing $18.00 bid #7), Party C (NDA 09/15), Party D (NDA 09/23), Party A (NDA 09/30). Contacted but never entered: Parties B, E, F</t>
+          <t>4 strategic: Ingredion (carried from round 0, in diligence), Party C (NDA 09/15), Party D (NDA 09/23), Party A (NDA 09/30). Parties B, E and F were contacted but never entered.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -3810,12 +4022,12 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2: Ingredion (#23, #31, #32); Party A (#44, received 10/14 after round 2 opened, answering Deutsche Bank’s 10/04 request)</t>
+          <t>1: Ingredion (09/17 $18.25–$18.50 oral; 10/02 $18.50 oral; 10/02 $19.00 letter). No proposal from Parties A, C or D in the round.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Board picked Ingredion for definitive negotiation 10/03 (#33). Market check left open: Party D withdrew 10/08; Party A (lower bid) and Party C (inactive) not selected at signing 10/14</t>
+          <t>10/03: Ingredion selected for definitive negotiation (one advanced). Party A still being received (round 2). Party D withdrew 10/08; Party C inferred not selected at signing.</t>
         </is>
       </c>
     </row>
@@ -3831,12 +4043,12 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Board directed management to negotiate and finalize a definitive agreement with Ingredion alone (#33, #34)</t>
+          <t>Board directed management to negotiate and finalize a definitive agreement with Ingredion (#38).</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>1 strategic: Ingredion. Still being received, not admitted: Party A (bid #44); Parties C and D remained under NDA in the market check</t>
+          <t>1 strategic: Ingredion. Then, still being received, not admitted: Party A (strategic).</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -3856,12 +4068,12 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>1: Ingredion ($19.00 reaffirmed by returned draft #39 and price confirmation #43)</t>
+          <t>2: Ingredion (10/14 reaffirmed $19.00), Party A (10/14 $16.00 letter).</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Signing with Ingredion at $19.00 cash, 10/14/2014 (#45)</t>
+          <t>signing with Ingredion 10/14/2014 at $19.00 cash; Party A not selected.</t>
         </is>
       </c>
     </row>
@@ -3877,14 +4089,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
@@ -3934,17 +4146,17 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Should Ingredion’s early price references count as bids: the 52-week high cited on 07/17 and the $17.00 suggested on 08/06?</t>
+          <t>Ingredion’s first price: on 07/17 Gordon cited no number, but the 09/29 board minutes call $16.00 (the 52-week high) Ingredion’s “initial indication”. Is 07/17 a Bid, and is the 08/06 $17.00 suggestion a Bid?</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>No for 07/17; yes for 08/06. #2 stays Bidder interest with no price; #6 stays an Informal $17.00 Bid.</t>
+          <t>Record 07/17 as Bidder interest (no price) and 08/06 $17.00 as the first, oral, Informal Bid.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>On 07/17 Gordon “did not cite a specific number” but noted the ~$16.00 52-week high (p. 24), a historical-price reference (C6). The board later called it “Ingredion’s initial indication of $16.00” (p. 30), but that label came afterwards. On 08/06 Fortnum put forward $17.00 as a price likely to win Ingredion board support (p. 25): a price was communicated, so C12 makes it a Bid.</t>
+          <t>Gordon “did not cite a specific number” (p. 24); Fortnum said Ingredion was “prepared to submit a proposal” and suggested $17.00 (p. 25); board’s “$16.00 (based on the 52-week high)” (p. 30).</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -3954,7 +4166,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Adding a $16.00 bid on 07/17 would start Ingredion’s price path at $16.00. Treating #6 as a non-offer would start it at $18.00 (#7). The round-0 bid count changes either way; nothing else does.</t>
+          <t>A $16.00 Bid on 07/17 would add a round-0 bid; dropping #6 would make the 08/10 $18.00 letter the first price.</t>
         </is>
       </c>
       <c r="G2" s="2" t="n"/>
@@ -3967,27 +4179,27 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Which parties make up Deutsche Bank’s “six potential strategic counterparties”, and is Party A inside that total?</t>
+          <t>Process and round map: one process; round 0 (Ingredion approach through the 08/28 decision), round 1 opened by the market-check outreach, round 2 opened 10/03 by definitive negotiation with Ingredion; announcement post. Is this the right map?</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>The six are Parties A–F. Party A counts, even though it first approached Penford itself on 08/01 (#8). No residual cohort row.</t>
+          <t>Yes. One process, rounds 0, 1, 2 as recorded. No bid due date was set in either round, so no deadline-outcome Question arises.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Page 28 says six were contacted in early to mid-September but names only A–E then. Party F was contacted 09/24 (#26). At signing Deutsche Bank tallied six: “two of which declined to enter into nondisclosure agreements” (B, F), one “never returned” a voicemail (E), and three that “did not move forward in a timely manner or made a lower indication” (A, C, D) (p. 32). The filing counts parties, not agreements.</t>
+          <t>E6 opens round 1 at the first outreach wave (p. 28); 10/03 board direction to finalize with Ingredion is a move to definitive negotiation (p. 31). Contacts run continuously 07/08–10/14/2014; no gap of about two months. E5: only one attempt; the 2007 and 2009 approaches are year-dated only (p. 23), so they go to Deal facts, and tests (a)–(c) never trigger a second process.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>#8, #16, #18, #19, #20, #21, #26, #28</t>
+          <t>#16, #26, #38</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>If the September “six” excludes Party F, there were seven contacts: add an unnamed, never-entered contact row (Count 1) and treat the p. 32 total as wrong. The auction screen (4 NDA parties) is unchanged either way.</t>
+          <t>Alternatives: round 1 opens 08/14 (target admits Ingredion to diligence) moving #11–#15 into round 1; or 08/28 decision date; or Ingredion’s 09/17 and 10/02 bids stay round-0 bargaining over #7, moving #26, #36, #37 to round 0.</t>
         </is>
       </c>
       <c r="G3" s="2" t="n"/>
@@ -4000,27 +4212,27 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Process and round map: one process, with round 0 (unsolicited Ingredion approach), round 1 (market check plus Ingredion negotiation) and round 2 (definitive negotiation with Ingredion). Is that right?</t>
+          <t>Outreach total: the filing says Deutsche Bank contacted six strategic parties “throughout early- to mid-September”, but Party F was contacted 09/24. Who are the six?</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Yes. Round 1 opens with the first outreach wave in early September (#16). Round 2 opens on the 10/03 decision to finalize with Ingredion (#33, #34). Party A’s 10/14 bid (#44) belongs to round 1. The 2007 and 2009 approaches are background, not processes. No round had a due date, so no deadline Question is needed.</t>
+          <t>The six are Parties A–F. The 10/14 breakdown (two declined NDAs, one unanswered voicemail, three remaining) fits B and F, E, and A, C, D exactly.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>C8 rule 1 puts round 1 at the first outreach wave (p. 28). A move to definitive negotiation with no earlier final round opens a new round, hence 10/03 (p. 31). #44 answers Deutsche Bank’s 10/04 market-check request (p. 31). No gap of two months or more without acquirer contact exists between 07/08 and 10/14; the longest is 07/23 to 08/01 (Party A’s email) or 08/05. C7 tests: (a) not met, since Ingredion was always live; (b) not met, no break; (c) not reached. The 2007/2009 approaches have a year only (p. 23).</t>
+          <t>p. 28 (six contacted early-to-mid September); p. 29 (Party F contacted 09/24); p. 32 (total of six, with breakdown).</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>#10, #16, #33, #34, #44</t>
+          <t>#16, #19, #20, #21, #22, #24, #29</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Most plausible alternative: round 1 opens 08/13–08/14, when the board chose to pursue Ingredion and began sharing information (bilateral negotiation start). That would move #10–#15 from round 0 into round 1. A second alternative puts #44 in round 2 as a late bid received during that stage.</t>
+          <t>If the September six exclude F, a seventh unnamed contact exists, contradicting the stated total of six; one Contact row (Count 1, Unknown type) would be added. The auction screen (4 NDA parties) is unaffected.</t>
         </is>
       </c>
       <c r="G4" s="2" t="n"/>
@@ -4033,27 +4245,27 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Late reconfirmation: Ingredion’s last priced bid (#32, $19.00) was Informal. Does the 10/08 returned draft make it Formal, and what conditions apply?</t>
+          <t>Ingredion’s adviser delivered its own draft merger agreement on 09/06 while the $18.00 indication stood. Does that make Ingredion’s 09/17 and 10/02 bids Formal under E11(1)?</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Yes. #39 is Bid reaffirmed by returned draft, Formal, Conditions Light. #43 is a second Bid reaffirmed by price confirmation, Formal, Conditions None.</t>
+          <t>No; keep them Informal. The draft was not put forward with or expressly in support of those prices, and the filing calls them revised indications of interest.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Test (a): on 10/03 the board directed finalizing with Ingredion (p. 31), with no further priced submission awaited. Test (b): #32 is Informal. Test (c): Sidley Austin returned a revised draft on 10/08 (p. 31), the bidder’s first act after 10/03. The earlier 10/06 counsel discussion was not a returned draft. On 10/14 Fortnum called “to confirm the proposed price of $19.00” (p. 32). There is no financing condition (p. 45).</t>
+          <t>Draft delivered 09/06 (p. 28); 09/17 “could potentially increase” (p. 29); 10/02 letter “regarding its indication of interest” (p. 30).</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>#32, #33, #39, #43</t>
+          <t>#18, #26, #36, #37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Conditions on #39 could instead be Unclear, given the open request for FY2014 financial statements as a closing condition and the 10/13 valuation warning. If the returned draft is not accepted as a reaffirmation, Ingredion’s first Formal row is #43.</t>
+          <t>Three Ingredion bids in round 1 become Formal (Conditions stay Unclear), so round 1 would contain formal bids and Ingredion would not need the reaffirmation row (#46).</t>
         </is>
       </c>
       <c r="G5" s="2" t="n"/>
@@ -4066,27 +4278,27 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Party A: are its 10/04 and 10/13 value statements bids, and is its 10/14 exit Not selected at signing?</t>
+          <t>Party A’s 10/04 statement (any offer below $17.50–$18.00, cash) and 10/13 reduced value range ($16.00–$18.00): Bids, or valuation statements without an offer?</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Record them as valuation statements (Other material event), not bids. The $16.00 letter (#44) is its only Bid and is Informal. The exit is Not selected at signing, for a lower offer than the rival’s.</t>
+          <t>Valuation statements (Other material event). Party A’s first proposal is its 10/14 “formal letter with its indication of interest” at $16.00, which Deutsche Bank had asked for on 10/04.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>On 10/04 Party A said only that “any offer would be below $17.50 - $18.00” (p. 31), and on 10/13 that its “value range” had changed (p. 32). Both are ceilings or ranges with no proposal attached, and Deutsche Bank was still asking for a letter. The letter itself was an “indication of interest” with no markup (p. 32); calling it a “formal letter” does not make it Formal under C13.</t>
+          <t>p. 31 (“any offer would be below”; Deutsche Bank “encouraged Party A to submit a letter of interest”); p. 32 (value range reduced; formal letter at $16.00).</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>#36, #42, #44, #46</t>
+          <t>#40, #45, #47</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>As bids, #36 and #42 would add two Informal Party A bids: #36 with Price high 17.50–18.00 or no price, #42 with range 16.00–18.00. Party A would then have bid in round 1 before 10/14. Live counts are unchanged.</t>
+          <t>Party A would gain two Informal bids in round 2: 10/13 with Price low 16.00 and Price high 18.00; 10/04 with no clean endpoint (Price high blank or 17.50–18.00 read as a ceiling).</t>
         </is>
       </c>
       <c r="G6" s="2" t="n"/>
@@ -4099,33 +4311,66 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Party C: when and how did its participation end?</t>
+          <t>Should Ingredion’s 10/14 confirmation of $19.00 be a Bid reaffirmed row?</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Not selected at signing, inferred, by 10/14 (#47).</t>
+          <t>Yes. Fortnum himself confirmed the price after the board moved to finalize with Ingredion (10/03), and its latest priced row (#37) is Informal, so the row adds Ingredion’s only Formal price.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Party C’s last reported step is the 09/25 management presentation (p. 29). At signing Deutsche Bank said the remaining three NDA signers “either did not move forward in a timely manner or made a lower indication of value” (p. 32). D withdrew (#40) and A bid lower (#44), so C is the one that did not move forward. The filing never says C withdrew or was dropped.</t>
+          <t>Fortnum “called Mr. Malkoski to confirm the proposed price of $19.00” (p. 32); board told price “remained at $19.00” (p. 32).</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>#47</t>
+          <t>#46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>If C is read as having withdrawn in early October, its exit becomes Withdrew. Round 2 would then open with Parties A and D as the only non-admitted live NDA holders, not A, C and D.</t>
+          <t>Without it, Ingredion has no Formal bid; signing (#48) would be the only record of a binding $19.00 commitment.</t>
         </is>
       </c>
       <c r="G7" s="2" t="n"/>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>How do Party C and Party A leave? Neither has a reported exit.</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Party C: inferred Not selected at signing, reason Not stated. Party A: Not selected at signing, Lower offer than rivals ($16.00 vs $19.00), not inferred since both offers are reported at signing.</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Deutsche Bank kept the market check running after 10/03 (Party A 10/04, Party D 10/08; p. 31), so 10/03 did not drop them. 10/14 report: remaining three “did not move forward in a timely manner or made a lower indication of value” (p. 32).</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>#50, #51</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Party C could instead be Dropped by target at 10/03 (round 1 advancement) or Withdrew (did not move forward); either changes the live count in round 2 and the exit’s valuation signal.</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G7"/>
+  <autoFilter ref="A1:G8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4163,7 +4408,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Penford Corporation</t>
+          <t>Penford Corporation (Washington corporation; specialty natural-based ingredients, Centennial, Colorado)</t>
         </is>
       </c>
     </row>
@@ -4187,7 +4432,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Strategic: a global manufacturer and supplier of starch and sweetener ingredients (p. 1)</t>
+          <t>Strategic: global manufacturer and supplier of starch and sweetener ingredients (pp. 1, 18).</t>
         </is>
       </c>
     </row>
@@ -4199,7 +4444,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>$19.00 per share in cash; no financing condition (p. 45)</t>
+          <t>$19.00 per share in cash, without interest; no financing condition, funded from available cash and revolver borrowings (p. 45). SEACOR (about 9.28%) voting and support agreement.</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4480,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>DEFM14A, 12/29/2014</t>
+          <t>DEFM14A (definitive proxy statement), dated 12/29/2014</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4504,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>bidder-led (Ingredion approached 07/08–07/17/2014; SEACOR’s concurrent 13D director nominations are not reported as pressing for a sale)</t>
+          <t>bidder-led</t>
         </is>
       </c>
     </row>
@@ -4283,7 +4528,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>2007 and 2009: unsolicited indications of interest from two parties in Penford’s industry. Penford signed a confidentiality agreement with each, held discussions and exchanged information; no offers resulted (p. 23). The agreements were not reused in 2014.</t>
+          <t>2007 and 2009: unsolicited indications of interest from two industry parties; confidentiality agreements and discussions, no offers (p. 23). Year-dated only, so no process rows.</t>
         </is>
       </c>
     </row>
@@ -4295,7 +4540,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Met (process 1): 4 parties: Ingredion, Party C, Party D, Party A. That is 5 agreements, since Ingredion’s 08/21 NDA superseded its 07/20 Secrecy Agreement. Deutsche Bank’s 09/24 report of NDAs with two counterparties plus one reviewing a draft matches C, D and A. No post-signing additions.</t>
+          <t>Met (process 1): 4 parties (Ingredion, Party C, Party D, Party A)</t>
         </is>
       </c>
     </row>
@@ -4319,7 +4564,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>US dollars per share (Ingredion’s on a fully diluted basis)</t>
+          <t>US dollars per share; Ingredion’s prices on a fully diluted basis.</t>
         </is>
       </c>
     </row>
@@ -4331,7 +4576,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Deutsche Bank (Deutsche Bank Securities Inc.), sole financial adviser and fairness opinion provider</t>
+          <t>Deutsche Bank Securities Inc.</t>
         </is>
       </c>
     </row>
@@ -4355,7 +4600,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Ingredion, a strategic buyer, approached Penford in July 2014 and signed a secrecy agreement. It offered $17.00 orally on 08/06 and an indicative $18.00 in cash on 08/10/2014. Penford refused exclusivity, gave Ingredion diligence access and authorized a Deutsche Bank market check. That check reached six strategic parties, of which Parties A, C and D signed NDAs. Ingredion moved to $18.25–$18.50 and then $19.00 on 10/02, and on 10/03 the board chose to finalize with it. Party D withdrew, Party C went quiet, and Party A’s best was a $16.00 indication on 10/14. Penford signed with Ingredion at $19.00 in cash on 10/14/2014, with SEACOR signing a voting agreement.</t>
+          <t>Ingredion’s CEO approached Penford in July 2014, amid SEACOR’s board nomination contest, and moved from an oral $17.00 suggestion to an $18.00 cash indication on 08/10. The board called that inadequate, refused exclusivity and gave Ingredion diligence access to win a higher price, while Deutsche Bank ran a market check of six strategic parties from September. Parties A, C and D signed NDAs; B and F declined, E never answered, and the board chose not to approach Party G. Ingredion edged up to $18.25–$18.50 and then $19.00 on 10/02, against the board’s wish for $20.00, and the board directed a definitive agreement on 10/03. Party D withdrew and Party A offered only $16.00, and Penford signed with Ingredion at $19.00 cash on 10/14/2014, with SEACOR’s voting support.</t>
         </is>
       </c>
     </row>

--- a/extraction/penford.xlsx
+++ b/extraction/penford.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deal facts" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Deal ledger'!$A$1:$V$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Deal ledger'!$A$1:$V$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Rounds'!$A$1:$J$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Questions'!$A$1:$G$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Deal facts'!$A$1:$B$18</definedName>
@@ -24,9 +24,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="MM/DD/YYYY"/>
+    <numFmt numFmtId="166" formatCode="$0.00"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -71,7 +72,7 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -439,19 +440,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V53"/>
+  <dimension ref="A1:V51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="7" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="7" customWidth="1" min="13" max="13"/>
@@ -589,10 +590,10 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>SEACOR</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n"/>
+          <t>SEACOR Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Activist</t>
@@ -606,20 +607,20 @@
       </c>
       <c r="H2" s="2" t="n"/>
       <c r="I2" s="2" t="n"/>
-      <c r="J2" s="2" t="n"/>
-      <c r="K2" s="2" t="n"/>
-      <c r="L2" s="2" t="n"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="n"/>
-      <c r="N2" s="2" t="n"/>
-      <c r="O2" s="2" t="n"/>
+      <c r="N2" s="2" t="inlineStr"/>
+      <c r="O2" s="2" t="inlineStr"/>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>SEACOR (about 9.28% holder; its representative Mr. Behrens sits on the board) amended its Schedule 13D announcing a board nomination contest for four seats; nominees named in 08/19/2014 amendment. Later signs voting and support agreement (#49).</t>
+          <t>SEACOR (about 9.28% holder) amends its Schedule 13D to announce a slate of four director nominees; nominees named 08/19/2014. Filing does not say SEACOR pressed for a sale. At signing SEACOR signs a voting and support agreement (see signing row).</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>SEACOR stated its intent to nominate four candidates for election as directors of our board at Penford’s next annual meeting of shareholders (p. 24)</t>
+          <t>“SEACOR stated its intent to nominate four candidates for election as directors of our board at Penford’s next annual meeting of shareholders” (p. 24)</t>
         </is>
       </c>
       <c r="R2" s="2" t="n"/>
@@ -666,29 +667,25 @@
       </c>
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N3" s="2" t="n"/>
-      <c r="O3" s="2" t="n"/>
+      <c r="N3" s="2" t="inlineStr"/>
+      <c r="O3" s="2" t="inlineStr"/>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>First contact: Ingredion CEO Gordon left voicemail 07/08/2014 seeking a meeting, purpose unstated. At 07/17 lunch she stated interest in acquiring Penford, cited no price; noted 52-week high about $16.00 and trading price about $12.00. CFO meeting 07/19 also named no price.</t>
+          <t>First contact: Ingredion CEO Gordon voicemail 07/08/2014 seeking a meeting (purpose not stated). At 07/17 lunch she states interest in acquiring Penford; no price, but cites 52-week high of about $16.00 and current price of about $12.00.</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>Ms. Gordon advised Mr. Malkoski of Ingredion’s interest in acquiring Penford (p. 24)</t>
-        </is>
-      </c>
-      <c r="R3" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
+          <t>“Ms. Gordon advised Mr. Malkoski of Ingredion’s interest in acquiring Penford” (p. 24)</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="n"/>
       <c r="S3" s="2" t="n"/>
       <c r="T3" s="3" t="n">
         <v>41837</v>
@@ -706,7 +703,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>effective 07/20/2014</t>
+          <t>07/19/2014</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -721,7 +718,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>NDA signed</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
@@ -732,34 +729,38 @@
       </c>
       <c r="H4" s="2" t="n"/>
       <c r="I4" s="2" t="n"/>
-      <c r="J4" s="2" t="n"/>
-      <c r="K4" s="2" t="n"/>
-      <c r="L4" s="2" t="n"/>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N4" s="2" t="n"/>
-      <c r="O4" s="2" t="n"/>
+      <c r="N4" s="2" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr"/>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Secrecy Agreement for limited exchange of confidential information; executed 'subsequently' to the 07/19 meeting, effective 07/20; execution day not stated, so Date to runs to its supersession on 08/21 (#13). Ingredion's entry.</t>
+          <t>Valuation statement without an offer: Ingredion CFO Fortnum names no price but says reaching the $16.00 52-week high could be a challenge given implied EV/EBITDA multiple; parties discuss using adjusted EBITDA and synergies to support valuation.</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Penford and Ingredion executed a Secrecy Agreement, effective as of July 20, 2014, providing for limited exchange of confidential information (p. 24)</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="n"/>
+          <t>“stating that it could be a challenge for Ingredion to reach this value given the implied enterprise value and EBITDA multiple at that price” (p. 24)</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="S4" s="2" t="n"/>
       <c r="T4" s="3" t="n">
-        <v>41840</v>
+        <v>41839</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>41840</v>
+        <v>41839</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>41872</v>
+        <v>41839</v>
       </c>
     </row>
     <row r="5">
@@ -768,18 +769,22 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>07/24/2014</t>
+          <t>effective 07/20/2014 (executed after the 07/19/2014 meeting)</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Perkins Coie LLP</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n"/>
+          <t>Ingredion</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Adviser</t>
+          <t>NDA signed</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
@@ -790,32 +795,34 @@
       </c>
       <c r="H5" s="2" t="n"/>
       <c r="I5" s="2" t="n"/>
-      <c r="J5" s="2" t="n"/>
-      <c r="K5" s="2" t="n"/>
-      <c r="L5" s="2" t="n"/>
-      <c r="M5" s="2" t="n"/>
-      <c r="N5" s="2" t="n"/>
-      <c r="O5" s="2" t="n"/>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr"/>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Penford's legal counsel; earliest shown acting at the 07/24/2014 Executive Committee meeting. Advised board on fiduciary duties and negotiated the merger agreement.</t>
+          <t>Ingredion’s entry: Secrecy Agreement, “effective as of July 20, 2014”, for a limited exchange of confidential information. Execution day not stated: after 07/19 and before its supersession on 08/21/2014; Sort date uses the stated effective date.</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>representatives of Perkins Coie LLP (referred to as Perkins Coie), Penford’s legal counsel, were present (p. 25)</t>
+          <t>“Subsequently, Penford and Ingredion executed a Secrecy Agreement, effective as of July 20, 2014, providing for limited exchange of confidential information” (p. 24)</t>
         </is>
       </c>
       <c r="R5" s="2" t="n"/>
       <c r="S5" s="2" t="n"/>
       <c r="T5" s="3" t="n">
-        <v>41844</v>
+        <v>41840</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>41844</v>
+        <v>41839</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>41844</v>
+        <v>41872</v>
       </c>
     </row>
     <row r="6">
@@ -829,10 +836,10 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Deutsche Bank</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n"/>
+          <t>Perkins Coie LLP</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Adviser</t>
@@ -846,20 +853,20 @@
       </c>
       <c r="H6" s="2" t="n"/>
       <c r="I6" s="2" t="n"/>
-      <c r="J6" s="2" t="n"/>
-      <c r="K6" s="2" t="n"/>
-      <c r="L6" s="2" t="n"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="n"/>
-      <c r="N6" s="2" t="n"/>
-      <c r="O6" s="2" t="n"/>
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr"/>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>Penford's financial adviser. Executive Committee directed management to retain it (interviews held earlier in July) to advise on shareholder matters and strategic alternatives; engagement letter executed 09/11/2014. Delivered fairness opinion 10/14/2014.</t>
+          <t>Penford’s legal counsel; earliest reported acting at the 07/24/2014 Executive Committee meeting; advised the board on fiduciary duties (08/28 and 10/14) and negotiated the merger agreement.</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>the Executive Committee directed management to proceed to retain Deutsche Bank as the Company’s financial advisor (p. 25)</t>
+          <t>“representatives of Perkins Coie LLP (referred to as Perkins Coie), Penford’s legal counsel, were present” (p. 25)</t>
         </is>
       </c>
       <c r="R6" s="2" t="n"/>
@@ -880,22 +887,18 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>08/06/2014</t>
+          <t>07/24/2014</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Ingredion</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Deutsche Bank Securities Inc.</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr"/>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Adviser</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
@@ -904,56 +907,34 @@
       <c r="G7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="I7" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" s="2" t="n"/>
-      <c r="O7" s="2" t="n"/>
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="n"/>
+      <c r="N7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr"/>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Unclear: no conditions reported; diligence not yet begun. Oral: CFO Fortnum said Ingredion prepared to submit a proposal and $17.00 fully diluted could likely get Ingredion board support. Malkoski said probably too low. Cash not stated.</t>
+          <t>Penford’s financial adviser: Executive Committee directs its retention after Ingredion’s oral indication, to advise on shareholder matters and evaluate strategic alternatives; engagement letter executed 09/11/2014. Ran the market check; gave the fairness opinion.</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>Mr. Fortnum suggested that a price of $17.00 per share on a fully diluted basis could likely get support from Ingredion’s board (p. 25)</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
+          <t>“the Executive Committee directed management to proceed to retain Deutsche Bank as the Company’s financial advisor” (p. 25)</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="n"/>
       <c r="S7" s="2" t="n"/>
       <c r="T7" s="3" t="n">
-        <v>41857</v>
+        <v>41844</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>41857</v>
+        <v>41844</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>41857</v>
+        <v>41844</v>
       </c>
     </row>
     <row r="8">
@@ -962,7 +943,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>08/10/2014</t>
+          <t>08/06/2014</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -987,14 +968,14 @@
         <v>0</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not stated</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1010,28 +991,32 @@
       <c r="M8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N8" s="2" t="n"/>
-      <c r="O8" s="2" t="n"/>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr"/>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Unclear: letter states no conditions; diligence then followed (#13, #17). Indicative $18.00 cash, fully diluted, for all stock; board called it non-binding. Ref: $12.10 close 08/08/2014; 49% premium.</t>
+          <t>No condition stated; diligence not yet begun (no NDA-level access until 08/21). Oral: Fortnum says Ingredion is prepared to submit a proposal and $17.00 per fully diluted share could likely get Ingredion board support. Malkoski replies it is probably not high enough.</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>providing an indicative valuation of $18.00 per share in cash for all of the outstanding capital stock of Penford on a fully diluted basis (p. 25)</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="n"/>
+          <t>“Mr. Fortnum suggested that a price of $17.00 per share on a fully diluted basis could likely get support from Ingredion’s board” (p. 25)</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="S8" s="2" t="n"/>
       <c r="T8" s="3" t="n">
-        <v>41861</v>
+        <v>41857</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>41861</v>
+        <v>41857</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>41861</v>
+        <v>41857</v>
       </c>
     </row>
     <row r="9">
@@ -1040,12 +1025,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>08/11/2014</t>
+          <t>08/10/2014</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Party A</t>
+          <t>Ingredion</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1055,7 +1040,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Bidder interest</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
@@ -1064,36 +1049,52 @@
       <c r="G9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="2" t="n"/>
-      <c r="I9" s="2" t="n"/>
-      <c r="J9" s="2" t="n"/>
-      <c r="K9" s="2" t="n"/>
-      <c r="L9" s="2" t="n"/>
+      <c r="H9" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
       <c r="M9" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N9" s="2" t="n"/>
-      <c r="O9" s="2" t="n"/>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr"/>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>First contact: representative of Party A (a company in the industry) emailed 08/01/2014 asking for a call. At 08/11 CEO meeting Party A informally raised interest in acquiring or combining; would value only at a typical premium to trading price, not strategic plan. No price.</t>
+          <t>No condition stated; narrative shows diligence still to come (presentation, dataroom, site visits); financing not stated. Written indication of interest, $18.00 cash per fully diluted share. Ref: $12.10 close 08/08/2014; 49% premium. Deutsche Bank calls it non-binding.</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>Party A’s Chief Executive Officer also informally discussed Party A’s potential interest in acquiring or combining with Penford (p. 26)</t>
+          <t>“providing an indicative valuation of $18.00 per share in cash for all of the outstanding capital stock of Penford on a fully diluted basis” (p. 25)</t>
         </is>
       </c>
       <c r="R9" s="2" t="n"/>
       <c r="S9" s="2" t="n"/>
       <c r="T9" s="3" t="n">
-        <v>41862</v>
+        <v>41861</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>41862</v>
+        <v>41861</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>41862</v>
+        <v>41861</v>
       </c>
     </row>
     <row r="10">
@@ -1102,22 +1103,22 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>08/12/2014</t>
+          <t>08/11/2014</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>SEACOR</t>
+          <t>Party A</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Target interest</t>
+          <t>Bidder interest</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
@@ -1128,34 +1129,34 @@
       </c>
       <c r="H10" s="2" t="n"/>
       <c r="I10" s="2" t="n"/>
-      <c r="J10" s="2" t="n"/>
-      <c r="K10" s="2" t="n"/>
-      <c r="L10" s="2" t="n"/>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N10" s="2" t="n"/>
-      <c r="O10" s="2" t="n"/>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr"/>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Executive Committee (08/11) had Chairman Hatfield ask SEACOR's board representative Behrens, as Deutsche Bank identified SEACOR as a possible acquirer. SEACOR not interested 'at that time'; reconfirmed 08/13. No NDA; never entered. Type not described in filing.</t>
+          <t>First contact: Party A representative emails Malkoski 08/01/2014 asking for a call (purpose not stated). At 08/11 meeting Party A CEO informally raises interest in acquiring or combining; would pay only a typical premium to current price, based on trailing results.</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>Mr. Behrens stated that SEACOR was not interested in participating in any potential sale process at that time (p. 26)</t>
+          <t>“Party A’s Chief Executive Officer also informally discussed Party A’s potential interest in acquiring or combining with Penford” (p. 26)</t>
         </is>
       </c>
       <c r="R10" s="2" t="n"/>
       <c r="S10" s="2" t="n"/>
       <c r="T10" s="3" t="n">
-        <v>41863</v>
+        <v>41862</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>41863</v>
+        <v>41862</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>41863</v>
+        <v>41862</v>
       </c>
     </row>
     <row r="11">
@@ -1164,18 +1165,22 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>08/13/2014</t>
+          <t>08/12/2014</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Penford</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n"/>
+          <t>SEACOR Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Target sale decision</t>
+          <t>Target interest</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
@@ -1186,32 +1191,34 @@
       </c>
       <c r="H11" s="2" t="n"/>
       <c r="I11" s="2" t="n"/>
-      <c r="J11" s="2" t="n"/>
-      <c r="K11" s="2" t="n"/>
-      <c r="L11" s="2" t="n"/>
-      <c r="M11" s="2" t="n"/>
-      <c r="N11" s="2" t="n"/>
-      <c r="O11" s="2" t="n"/>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr"/>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Board directed management to further investigate and develop Ingredion's proposal (Executive Committee reached the same view 08/11). A 'market check' of other counterparties was contemplated only if progress was made and an acceptable price received.</t>
+          <t>Executive Committee (08/11), after Deutsche Bank named SEACOR a potential counterparty, has Chairman Hatfield ask SEACOR director Behrens; SEACOR not interested “at that time”, confirmed at 08/13 board. SEACOR never enters. Type: filing does not describe SEACOR’s business.</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>the board members present at the meeting unanimously directed management to proceed with further investigation and development of the proposal from Ingredion (p. 26)</t>
+          <t>“Mr. Behrens stated that SEACOR was not interested in participating in any potential sale process at that time” (p. 26)</t>
         </is>
       </c>
       <c r="R11" s="2" t="n"/>
       <c r="S11" s="2" t="n"/>
       <c r="T11" s="3" t="n">
-        <v>41864</v>
+        <v>41863</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>41864</v>
+        <v>41863</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>41864</v>
+        <v>41863</v>
       </c>
     </row>
     <row r="12">
@@ -1220,7 +1227,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>08/14/2014</t>
+          <t>08/13/2014</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1228,10 +1235,10 @@
           <t>Penford</t>
         </is>
       </c>
-      <c r="D12" s="2" t="n"/>
+      <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Target sale decision</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
@@ -1242,32 +1249,36 @@
       </c>
       <c r="H12" s="2" t="n"/>
       <c r="I12" s="2" t="n"/>
-      <c r="J12" s="2" t="n"/>
-      <c r="K12" s="2" t="n"/>
-      <c r="L12" s="2" t="n"/>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="n"/>
-      <c r="N12" s="2" t="n"/>
-      <c r="O12" s="2" t="n"/>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr"/>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>Rejected $18.00 as not reflecting full value; board authorized engagement and information sharing so Ingredion would raise its price; management presentation set for 08/21 and diligence process discussed.</t>
+          <t>Board directs further investigation and development of Ingredion’s proposal (following the Executive Committee’s 08/11 determination). A “market check” of other counterparties is discussed only if progress is made with Ingredion and an acceptable price is received.</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>the board authorized management to engage with Ingredion and provide additional information regarding the Company (p. 27)</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="n"/>
+          <t>“the board members present at the meeting unanimously directed management to proceed with further investigation and development of the proposal from Ingredion” (p. 26)</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
       <c r="S12" s="2" t="n"/>
       <c r="T12" s="3" t="n">
-        <v>41865</v>
+        <v>41864</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>41865</v>
+        <v>41864</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>41865</v>
+        <v>41864</v>
       </c>
     </row>
     <row r="13">
@@ -1281,17 +1292,13 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Ingredion</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Penford</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Exclusivity changed</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F13" s="2" t="n">
@@ -1302,25 +1309,27 @@
       </c>
       <c r="H13" s="2" t="n"/>
       <c r="I13" s="2" t="n"/>
-      <c r="J13" s="2" t="n"/>
-      <c r="K13" s="2" t="n"/>
-      <c r="L13" s="2" t="n"/>
-      <c r="M13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" s="2" t="n"/>
-      <c r="O13" s="2" t="n"/>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="n"/>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr"/>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Requested: Ingredion asked whether Penford would consider exclusive negotiations; Penford declined as status and price did not justify it. Penford again declined exclusivity on 08/20–08/21/2014. No exclusivity was ever granted.</t>
+          <t>Target response: Malkoski tells Ingredion the $18.00 proposal does not reflect full value; board authorizes engagement and information sharing to get Ingredion to raise its price; management presentation set for 08/21/2014.</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>Mr. Malkoski indicated that the current status of negotiations and the proposed price did not justify providing exclusivity (p. 27)</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="n"/>
+          <t>“the board authorized management to engage with Ingredion and provide additional information regarding the Company, which the board believed would assist Ingredion in recognizing Penford’s additional value” (p. 27)</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
       <c r="S13" s="2" t="n"/>
       <c r="T13" s="3" t="n">
         <v>41865</v>
@@ -1338,7 +1347,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>08/21/2014</t>
+          <t>08/14/2014</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1353,7 +1362,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Exclusivity changed</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
@@ -1364,34 +1373,38 @@
       </c>
       <c r="H14" s="2" t="n"/>
       <c r="I14" s="2" t="n"/>
-      <c r="J14" s="2" t="n"/>
-      <c r="K14" s="2" t="n"/>
-      <c r="L14" s="2" t="n"/>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N14" s="2" t="n"/>
-      <c r="O14" s="2" t="n"/>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr"/>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Executed nondisclosure and standstill agreement superseding the Secrecy Agreement (#3); same day, management presentation to Ingredion and J.P. Morgan with historical results and financial projections. Ingredion was then the only party under NDA.</t>
+          <t>Exclusivity requested by Ingredion and declined by Penford (status and price did not justify it); Penford declines again during 08/20–08/21/2014 NDA negotiations. No exclusivity was ever executed.</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>On August 21, 2014, Ingredion and Penford executed a nondisclosure and standstill agreement that superseded the prior Secrecy Agreement. (p. 27)</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="n"/>
+          <t>“Mr. Malkoski indicated that the current status of negotiations and the proposed price did not justify providing exclusivity.” (p. 27)</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
       <c r="S14" s="2" t="n"/>
       <c r="T14" s="3" t="n">
-        <v>41872</v>
+        <v>41865</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>41872</v>
+        <v>41865</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>41872</v>
+        <v>41865</v>
       </c>
     </row>
     <row r="15">
@@ -1405,13 +1418,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>J.P. Morgan Securities</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="n"/>
+          <t>Ingredion</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Adviser</t>
+          <t>NDA signed</t>
         </is>
       </c>
       <c r="F15" s="2" t="n">
@@ -1422,23 +1439,29 @@
       </c>
       <c r="H15" s="2" t="n"/>
       <c r="I15" s="2" t="n"/>
-      <c r="J15" s="2" t="n"/>
-      <c r="K15" s="2" t="n"/>
-      <c r="L15" s="2" t="n"/>
-      <c r="M15" s="2" t="n"/>
-      <c r="N15" s="2" t="n"/>
-      <c r="O15" s="2" t="n"/>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr"/>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>Ingredion's financial adviser; earliest shown acting at the 08/21/2014 management presentation. Delivered Ingredion's draft merger agreement 09/06 (#18).</t>
+          <t>Nondisclosure and standstill agreement superseding the 07/20 Secrecy Agreement; adds a standstill. Not a new entry: Ingredion entered at the Secrecy Agreement row.</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>representatives of J.P. Morgan Securities, Ingredion’s financial advisor (p. 27)</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="n"/>
+          <t>“On August 21, 2014, Ingredion and Penford executed a nondisclosure and standstill agreement that superseded the prior Secrecy Agreement.” (p. 27)</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
       <c r="S15" s="2" t="n"/>
       <c r="T15" s="3" t="n">
         <v>41872</v>
@@ -1456,18 +1479,18 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>08/28/2014</t>
+          <t>08/21/2014</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Penford</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="n"/>
+          <t>J.P. Morgan Securities</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Target sale decision</t>
+          <t>Adviser</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
@@ -1478,32 +1501,32 @@
       </c>
       <c r="H16" s="2" t="n"/>
       <c r="I16" s="2" t="n"/>
-      <c r="J16" s="2" t="n"/>
-      <c r="K16" s="2" t="n"/>
-      <c r="L16" s="2" t="n"/>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="n"/>
-      <c r="N16" s="2" t="n"/>
-      <c r="O16" s="2" t="n"/>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr"/>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Board directed continued negotiation and diligence with Ingredion and authorized Deutsche Bank to run a 'market check': CEO-level inquiries to selected companies, substantive information only under an acceptable NDA. Launches the outreach in #16.</t>
+          <t>Ingredion’s financial adviser; earliest reported acting at the 08/21/2014 management presentation. Delivered Ingredion’s draft merger agreement to Deutsche Bank on 09/06/2014.</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>The board also authorized management and Deutsche Bank to proceed with the market check process as described at the meeting. (p. 27)</t>
+          <t>“representatives of J.P. Morgan Securities, Ingredion’s financial advisor” (p. 27)</t>
         </is>
       </c>
       <c r="R16" s="2" t="n"/>
       <c r="S16" s="2" t="n"/>
       <c r="T16" s="3" t="n">
-        <v>41879</v>
+        <v>41872</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>41879</v>
+        <v>41872</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>41879</v>
+        <v>41872</v>
       </c>
     </row>
     <row r="17">
@@ -1512,58 +1535,64 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>early-to-mid September 2014</t>
+          <t>08/21/2014</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Penford</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="n"/>
+          <t>Ingredion</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Round opened</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" s="2" t="n"/>
       <c r="I17" s="2" t="n"/>
-      <c r="J17" s="2" t="n"/>
-      <c r="K17" s="2" t="n"/>
-      <c r="L17" s="2" t="n"/>
-      <c r="M17" s="2" t="n"/>
-      <c r="N17" s="2" t="n"/>
-      <c r="O17" s="2" t="n"/>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr"/>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>Deutsche Bank market check: contacted six strategic counterparties to gauge interest while Ingredion continued diligence. First contacts reported 09/09 bound the start. Ingredion (live since #3) carried in; no bid due date set.</t>
+          <t>Information access: management presentation to Ingredion and J.P. Morgan (operations, strategy, historical financials and projections). Ingredion was then the only party under NDA; later NDA signers got the Strategic Plan projections (p. 43) but only Party C also had a presentation.</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>Deutsche Bank contacted six potential strategic counterparties in the same or similar industries to gauge initial interest regarding a potential transaction with Penford (p. 28)</t>
+          <t>“members of Penford’s management team provided a presentation to Ms. Gordon, Mr. Fortnum, and certain other members of Ingredion’s senior management” (p. 27)</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>Q2; Q3</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="S17" s="2" t="n"/>
       <c r="T17" s="3" t="n">
-        <v>41887</v>
+        <v>41872</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>41883</v>
+        <v>41872</v>
       </c>
       <c r="V17" s="3" t="n">
-        <v>41891</v>
+        <v>41872</v>
       </c>
     </row>
     <row r="18">
@@ -1572,60 +1601,58 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>early September 2014</t>
+          <t>08/28/2014</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Ingredion</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Penford</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Target sale decision</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18" s="2" t="n"/>
       <c r="I18" s="2" t="n"/>
-      <c r="J18" s="2" t="n"/>
-      <c r="K18" s="2" t="n"/>
-      <c r="L18" s="2" t="n"/>
-      <c r="M18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N18" s="2" t="n"/>
-      <c r="O18" s="2" t="n"/>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="n"/>
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr"/>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Information access: Ingredion alone given online dataroom access, plus calls, meetings and site visits to encourage it to improve its terms. No dataroom or site visits reported for Parties A, C or D.</t>
+          <t>Board directs continued negotiation and diligence with Ingredion and authorizes a Deutsche Bank “market check” of companies other than Ingredion, approached via their CEOs, with information exchanged only under an acceptable NDA. Strategic Plan last updated this day (p. 43).</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>Starting in early September, Penford provided Ingredion access to an online dataroom to review due diligence materials (p. 28)</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="n"/>
+          <t>“The board also authorized management and Deutsche Bank to proceed with the market check process as described at the meeting.” (p. 27)</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
       <c r="S18" s="2" t="n"/>
       <c r="T18" s="3" t="n">
-        <v>41887</v>
+        <v>41879</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>41883</v>
+        <v>41879</v>
       </c>
       <c r="V18" s="3" t="n">
-        <v>41892</v>
+        <v>41879</v>
       </c>
     </row>
     <row r="19">
@@ -1634,22 +1661,18 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>09/06/2014</t>
+          <t>early September 2014 (outreach “early- to mid-September”)</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Ingredion</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Penford</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr"/>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Round opened</t>
         </is>
       </c>
       <c r="F19" s="2" t="n">
@@ -1660,38 +1683,36 @@
       </c>
       <c r="H19" s="2" t="n"/>
       <c r="I19" s="2" t="n"/>
-      <c r="J19" s="2" t="n"/>
-      <c r="K19" s="2" t="n"/>
-      <c r="L19" s="2" t="n"/>
-      <c r="M19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N19" s="2" t="n"/>
-      <c r="O19" s="2" t="n"/>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="n"/>
+      <c r="N19" s="2" t="inlineStr"/>
+      <c r="O19" s="2" t="inlineStr"/>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Ingredion (through J.P. Morgan) delivered its initial draft merger agreement, contemplating voting and support agreements by significant shareholders; standing offer then $18.00 (#7). No new price.</t>
+          <t>Round 1 = first outreach wave: Deutsche Bank contacts strategic counterparties to gauge interest, executing the 08/28 authorization; no bid terms or due date stated. Ingredion continues in parallel. Window ends 09/09, by which Parties A and B had been contacted.</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>J.P. Morgan Securities provided Deutsche Bank with an initial draft of a merger agreement (p. 28)</t>
+          <t>“Deutsche Bank contacted six potential strategic counterparties in the same or similar industries to gauge initial interest regarding a potential transaction with Penford” (p. 28)</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q2; Q3</t>
         </is>
       </c>
       <c r="S19" s="2" t="n"/>
       <c r="T19" s="3" t="n">
-        <v>41888</v>
+        <v>41887</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>41888</v>
+        <v>41883</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>41888</v>
+        <v>41891</v>
       </c>
     </row>
     <row r="20">
@@ -1700,12 +1721,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>09/09/2014</t>
+          <t>early September 2014</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Party A</t>
+          <t>Ingredion</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1715,7 +1736,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
@@ -1726,38 +1747,34 @@
       </c>
       <c r="H20" s="2" t="n"/>
       <c r="I20" s="2" t="n"/>
-      <c r="J20" s="2" t="n"/>
-      <c r="K20" s="2" t="n"/>
-      <c r="L20" s="2" t="n"/>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N20" s="2" t="n"/>
-      <c r="O20" s="2" t="n"/>
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr"/>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Deutsche Bank market-check contact (target-initiated); Party A expressed interest in further discussions and was sent an NDA and standstill. Party A had first approached Penford 08/01 (#8); listed here to reconcile the six contacted.</t>
+          <t>Information access: Penford gives Ingredion alone an online dataroom, calls, meetings and site visits, to encourage it to improve its terms. No other party is reported to have received dataroom access.</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>On September 9, 2014, Party A expressed interest in having further discussions regarding a transaction (p. 28)</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>Q3</t>
-        </is>
-      </c>
+          <t>“Starting in early September, Penford provided Ingredion access to an online dataroom to review due diligence materials” (p. 28)</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="n"/>
       <c r="S20" s="2" t="n"/>
       <c r="T20" s="3" t="n">
-        <v>41891</v>
+        <v>41887</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>41891</v>
+        <v>41883</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>41891</v>
+        <v>41892</v>
       </c>
     </row>
     <row r="21">
@@ -1766,12 +1783,12 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>09/09/2014</t>
+          <t>early–mid September 2014; interest expressed 09/09/2014</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Party B</t>
+          <t>Party A</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1792,22 +1809,22 @@
       </c>
       <c r="H21" s="2" t="n"/>
       <c r="I21" s="2" t="n"/>
-      <c r="J21" s="2" t="n"/>
-      <c r="K21" s="2" t="n"/>
-      <c r="L21" s="2" t="n"/>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr"/>
       <c r="M21" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N21" s="2" t="n"/>
-      <c r="O21" s="2" t="n"/>
+      <c r="N21" s="2" t="inlineStr"/>
+      <c r="O21" s="2" t="inlineStr"/>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Target-initiated (Deutsche Bank market check). Party B expressed interest and was sent an NDA and standstill; declined 09/12 (#23).</t>
+          <t>Target-initiated (Deutsche Bank outreach) re-contact of Party A, which had approached in round 0; Party A expresses interest and is sent an NDA. One of the six outreach contacts.</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>another strategic counterparty contacted by Deutsche Bank (referred to as Party B) expressed interest in further discussions (p. 28)</t>
+          <t>“On September 9, 2014, Party A expressed interest in having further discussions regarding a transaction and Deutsche Bank forwarded Party A a nondisclosure and standstill agreement.” (p. 28)</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
@@ -1820,7 +1837,7 @@
         <v>41891</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>41891</v>
+        <v>41883</v>
       </c>
       <c r="V21" s="3" t="n">
         <v>41891</v>
@@ -1832,12 +1849,12 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>09/10/2014</t>
+          <t>early–mid September 2014; interest expressed 09/09/2014</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Party C</t>
+          <t>Party B</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1858,22 +1875,22 @@
       </c>
       <c r="H22" s="2" t="n"/>
       <c r="I22" s="2" t="n"/>
-      <c r="J22" s="2" t="n"/>
-      <c r="K22" s="2" t="n"/>
-      <c r="L22" s="2" t="n"/>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr"/>
       <c r="M22" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N22" s="2" t="n"/>
-      <c r="O22" s="2" t="n"/>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr"/>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>Target-initiated (Deutsche Bank market check). Party C expressed interest in pursuing a transaction; NDA and standstill forwarded 09/11/2014.</t>
+          <t>Target-initiated (Deutsche Bank outreach); Party B expresses interest and is sent an NDA. One of the six outreach contacts.</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>a third potential strategic counterparty contacted by Deutsche Bank (referred to as Party C) expressed interest in pursuing a transaction (p. 28)</t>
+          <t>“another strategic counterparty contacted by Deutsche Bank (referred to as Party B) expressed interest in further discussions” (p. 28)</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
@@ -1883,13 +1900,13 @@
       </c>
       <c r="S22" s="2" t="n"/>
       <c r="T22" s="3" t="n">
-        <v>41892</v>
+        <v>41891</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>41892</v>
+        <v>41883</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>41892</v>
+        <v>41891</v>
       </c>
     </row>
     <row r="23">
@@ -1898,12 +1915,12 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>09/11/2014</t>
+          <t>early–mid September 2014; interest expressed 09/10/2014</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Party D</t>
+          <t>Party C</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1924,22 +1941,22 @@
       </c>
       <c r="H23" s="2" t="n"/>
       <c r="I23" s="2" t="n"/>
-      <c r="J23" s="2" t="n"/>
-      <c r="K23" s="2" t="n"/>
-      <c r="L23" s="2" t="n"/>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
       <c r="M23" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N23" s="2" t="n"/>
-      <c r="O23" s="2" t="n"/>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr"/>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>Target-initiated (Deutsche Bank market check). Party D expressed interest; NDA and standstill forwarded.</t>
+          <t>Target-initiated (Deutsche Bank outreach); Party C expresses interest in pursuing a transaction; NDA sent 09/11/2014. One of the six outreach contacts.</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>a fourth potential strategic counterparty contacted by Deutsche Bank (referred to as Party D) expressed interest (p. 28)</t>
+          <t>“a third potential strategic counterparty contacted by Deutsche Bank (referred to as Party C) expressed interest in pursuing a transaction” (p. 28)</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
@@ -1949,13 +1966,13 @@
       </c>
       <c r="S23" s="2" t="n"/>
       <c r="T23" s="3" t="n">
-        <v>41893</v>
+        <v>41892</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>41893</v>
+        <v>41883</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>41893</v>
+        <v>41892</v>
       </c>
     </row>
     <row r="24">
@@ -1964,12 +1981,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>09/12/2014</t>
+          <t>early–mid September 2014; interest expressed 09/11/2014</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Party B</t>
+          <t>Party D</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1979,7 +1996,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
@@ -1990,34 +2007,38 @@
       </c>
       <c r="H24" s="2" t="n"/>
       <c r="I24" s="2" t="n"/>
-      <c r="J24" s="2" t="n"/>
-      <c r="K24" s="2" t="n"/>
-      <c r="L24" s="2" t="n"/>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N24" s="2" t="n"/>
-      <c r="O24" s="2" t="n"/>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr"/>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>Declined: Party B told Deutsche Bank it would not move forward or sign an NDA. Never entered, so no exit row; one of the two parties that declined NDAs (10/14 report).</t>
+          <t>Target-initiated (Deutsche Bank outreach); Party D expresses interest and is sent an NDA. One of the six outreach contacts.</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>Party B informed Deutsche Bank that it had decided not to move forward with discussions or sign a nondisclosure agreement (p. 28)</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="n"/>
+          <t>“a fourth potential strategic counterparty contacted by Deutsche Bank (referred to as Party D) expressed interest” (p. 28)</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
       <c r="S24" s="2" t="n"/>
       <c r="T24" s="3" t="n">
-        <v>41894</v>
+        <v>41893</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>41894</v>
+        <v>41883</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>41894</v>
+        <v>41893</v>
       </c>
     </row>
     <row r="25">
@@ -2031,7 +2052,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Party E</t>
+          <t>Party B</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -2041,7 +2062,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F25" s="2" t="n">
@@ -2052,29 +2073,25 @@
       </c>
       <c r="H25" s="2" t="n"/>
       <c r="I25" s="2" t="n"/>
-      <c r="J25" s="2" t="n"/>
-      <c r="K25" s="2" t="n"/>
-      <c r="L25" s="2" t="n"/>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N25" s="2" t="n"/>
-      <c r="O25" s="2" t="n"/>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr"/>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>Target-initiated: Deutsche Bank voicemail; several more voicemails over the next two weeks drew no response. Never entered.</t>
+          <t>Party B declines to continue or sign an NDA. It never entered, so no exit row. Counted by Deutsche Bank among two contacts that declined NDAs.</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>Deutsche Bank left a voicemail for another strategic counterparty (referred to as Party E) regarding a potential transaction (p. 28)</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>Q3</t>
-        </is>
-      </c>
+          <t>“Party B informed Deutsche Bank that it had decided not to move forward with discussions or sign a nondisclosure agreement” (p. 28)</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="n"/>
       <c r="S25" s="2" t="n"/>
       <c r="T25" s="3" t="n">
         <v>41894</v>
@@ -2092,12 +2109,12 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>09/15/2014</t>
+          <t>09/12/2014</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Party C</t>
+          <t>Party E</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -2107,7 +2124,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>NDA signed</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
@@ -2118,34 +2135,38 @@
       </c>
       <c r="H26" s="2" t="n"/>
       <c r="I26" s="2" t="n"/>
-      <c r="J26" s="2" t="n"/>
-      <c r="K26" s="2" t="n"/>
-      <c r="L26" s="2" t="n"/>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N26" s="2" t="n"/>
-      <c r="O26" s="2" t="n"/>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr"/>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>NDA with standstill that falls away on announcement of a definitive sale agreement. Penford supplied information including strategy, segments, historical results and financial projections. Party C's entry.</t>
+          <t>Target-initiated: Deutsche Bank voicemail to Party E; several more voicemails over the next two weeks go unanswered. Party E never responds or enters. One of the six outreach contacts.</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>On September 15, 2014, Penford and Party C executed a nondisclosure and standstill agreement (p. 28)</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="n"/>
+          <t>“Deutsche Bank left a voicemail for another strategic counterparty (referred to as Party E) regarding a potential transaction” (p. 28)</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
       <c r="S26" s="2" t="n"/>
       <c r="T26" s="3" t="n">
-        <v>41897</v>
+        <v>41894</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>41897</v>
+        <v>41894</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>41897</v>
+        <v>41894</v>
       </c>
     </row>
     <row r="27">
@@ -2154,12 +2175,12 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>09/17/2014</t>
+          <t>09/15/2014</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Ingredion</t>
+          <t>Party C</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -2169,7 +2190,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>NDA signed</t>
         </is>
       </c>
       <c r="F27" s="2" t="n">
@@ -2178,56 +2199,36 @@
       <c r="G27" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H27" s="4" t="n">
-        <v>18.25</v>
-      </c>
-      <c r="I27" s="4" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
+      <c r="H27" s="2" t="n"/>
+      <c r="I27" s="2" t="n"/>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N27" s="2" t="n"/>
-      <c r="O27" s="2" t="n"/>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr"/>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>Unclear: diligence and facility visits still being scheduled; no condition stated. Oral, tentative: 'could potentially increase' from $18.00 to $18.25 or $18.50, fully diluted, after Ingredion board meeting 09/16. Ref: $14.70 close 09/16/2014; 24%/26% premium.</t>
+          <t>Party C’s entry: NDA with standstill that falls away on announcement of a definitive sale agreement. Penford gives Party C strategy, segment, operations, historical financials and projections the same day.</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>Ingredion could potentially increase its proposal from $18.00 to $18.25 or $18.50 per share on a fully diluted basis (p. 29)</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>Q2; Q4</t>
-        </is>
-      </c>
+          <t>“On September 15, 2014, Penford and Party C executed a nondisclosure and standstill agreement” (p. 28)</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="n"/>
       <c r="S27" s="2" t="n"/>
       <c r="T27" s="3" t="n">
-        <v>41899</v>
+        <v>41897</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>41899</v>
+        <v>41897</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>41899</v>
+        <v>41897</v>
       </c>
     </row>
     <row r="28">
@@ -2236,12 +2237,12 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>09/23/2014</t>
+          <t>09/17/2014</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Party D</t>
+          <t>Ingredion</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -2251,7 +2252,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>NDA signed</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
@@ -2260,36 +2261,56 @@
       <c r="G28" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H28" s="2" t="n"/>
-      <c r="I28" s="2" t="n"/>
-      <c r="J28" s="2" t="n"/>
-      <c r="K28" s="2" t="n"/>
-      <c r="L28" s="2" t="n"/>
+      <c r="H28" s="4" t="n">
+        <v>18.25</v>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
       <c r="M28" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N28" s="2" t="n"/>
-      <c r="O28" s="2" t="n"/>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr"/>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>NDA with standstill that falls away on announcement of a definitive sale agreement. Party D's entry; no information delivery reported.</t>
+          <t>No condition stated; diligence and site visits still under way. Oral, after Ingredion’s 09/16 board meeting: could “potentially” raise from $18.00 to $18.25 or $18.50 per fully diluted share. Ref: $14.70 close 09/16/2014; 24%/26% premium. Executive Committee disappointed (09/19, told 09/23).</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>On September 23, 2014, Penford and Party D executed a nondisclosure and standstill agreement (p. 29)</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="n"/>
+          <t>“Mr. Fortnum indicated during the conversation that Ingredion could potentially increase its proposal from $18.00 to $18.25 or $18.50 per share on a fully diluted basis” (p. 29)</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
       <c r="S28" s="2" t="n"/>
       <c r="T28" s="3" t="n">
-        <v>41905</v>
+        <v>41899</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>41905</v>
+        <v>41899</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>41905</v>
+        <v>41899</v>
       </c>
     </row>
     <row r="29">
@@ -2298,18 +2319,22 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>09/24/2014</t>
+          <t>09/23/2014</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Penford</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="n"/>
+          <t>Party D</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>NDA signed</t>
         </is>
       </c>
       <c r="F29" s="2" t="n">
@@ -2320,32 +2345,34 @@
       </c>
       <c r="H29" s="2" t="n"/>
       <c r="I29" s="2" t="n"/>
-      <c r="J29" s="2" t="n"/>
-      <c r="K29" s="2" t="n"/>
-      <c r="L29" s="2" t="n"/>
-      <c r="M29" s="2" t="n"/>
-      <c r="N29" s="2" t="n"/>
-      <c r="O29" s="2" t="n"/>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr"/>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>Admission decision: board had Deutsche Bank approach Party F but not Party G (the two largest industry companies), citing interest, timing and confidentiality/misuse risk. Deutsche Bank reported market interest 'not particularly strong'. Party G reconsidered 10/03, not contacted.</t>
+          <t>Party D’s entry: NDA with standstill that falls away on announcement of a definitive sale agreement. Per p. 43, NDA signers received the Strategic Plan projections; no presentation to Party D is reported.</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>The board determined that Party F should be approached regarding a potential transaction with Penford, but due to the factors noted above, Party G should not be contacted. (p. 29)</t>
+          <t>“On September 23, 2014, Penford and Party D executed a nondisclosure and standstill agreement” (p. 29)</t>
         </is>
       </c>
       <c r="R29" s="2" t="n"/>
       <c r="S29" s="2" t="n"/>
       <c r="T29" s="3" t="n">
-        <v>41906</v>
+        <v>41905</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>41906</v>
+        <v>41905</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>41906</v>
+        <v>41905</v>
       </c>
     </row>
     <row r="30">
@@ -2359,17 +2386,13 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Party F</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Penford</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr"/>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
@@ -2380,29 +2403,23 @@
       </c>
       <c r="H30" s="2" t="n"/>
       <c r="I30" s="2" t="n"/>
-      <c r="J30" s="2" t="n"/>
-      <c r="K30" s="2" t="n"/>
-      <c r="L30" s="2" t="n"/>
-      <c r="M30" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N30" s="2" t="n"/>
-      <c r="O30" s="2" t="n"/>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="n"/>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr"/>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>Target-initiated: Deutsche Bank contacted Party F, one of the two largest companies in Penford's industry, on the board's authorization.</t>
+          <t>Admission decision: board decides to approach Party F, one of the two largest industry companies, but not Party G, citing confidentiality and misuse risks. Deutsche Bank reports two NDAs signed, a third under review, and interest “not particularly strong”.</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>On September 24, 2014, in accordance with the board’s authorization, Deutsche Bank contacted Party F regarding a potential transaction with Penford. (p. 29)</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>Q3</t>
-        </is>
-      </c>
+          <t>“The board determined that Party F should be approached regarding a potential transaction with Penford, but due to the factors noted above, Party G should not be contacted.” (p. 29)</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="n"/>
       <c r="S30" s="2" t="n"/>
       <c r="T30" s="3" t="n">
         <v>41906</v>
@@ -2420,12 +2437,12 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>09/25/2014</t>
+          <t>09/24/2014</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Party C</t>
+          <t>Party F</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2435,7 +2452,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="F31" s="2" t="n">
@@ -2446,34 +2463,38 @@
       </c>
       <c r="H31" s="2" t="n"/>
       <c r="I31" s="2" t="n"/>
-      <c r="J31" s="2" t="n"/>
-      <c r="K31" s="2" t="n"/>
-      <c r="L31" s="2" t="n"/>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N31" s="2" t="n"/>
-      <c r="O31" s="2" t="n"/>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr"/>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>Information access: in-person management presentation to Party C (operations, strategy, financial performance and projections). Party A was later refused one unless its price was competitive (#34); none reported for Party D.</t>
+          <t>Target-initiated: Deutsche Bank contacts Party F under the same-day board authorization. Party F is counted in the 10/14 total of six contacted.</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>members of Penford’s management team provided a presentation to Party C (p. 29)</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="n"/>
+          <t>“Deutsche Bank contacted Party F regarding a potential transaction with Penford.” (p. 29)</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
       <c r="S31" s="2" t="n"/>
       <c r="T31" s="3" t="n">
-        <v>41907</v>
+        <v>41906</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>41907</v>
+        <v>41906</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>41907</v>
+        <v>41906</v>
       </c>
     </row>
     <row r="32">
@@ -2482,12 +2503,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>09/29/2014</t>
+          <t>09/25/2014</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Party F</t>
+          <t>Party C</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2508,34 +2529,34 @@
       </c>
       <c r="H32" s="2" t="n"/>
       <c r="I32" s="2" t="n"/>
-      <c r="J32" s="2" t="n"/>
-      <c r="K32" s="2" t="n"/>
-      <c r="L32" s="2" t="n"/>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N32" s="2" t="n"/>
-      <c r="O32" s="2" t="n"/>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr"/>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>Declined: Party F said a combination was not a suitable strategic fit and declined further discussions. Never signed an NDA, so no exit row.</t>
+          <t>Information access: management presentation to Party C (operations, specialty products, technology, strategy, financial performance and projections). Only Ingredion and Party C received presentations; Party A was refused one (09/30).</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>Party F communicated to Deutsche Bank that a combination with Penford was not a suitable strategic fit and declined to pursue further discussions (p. 30)</t>
+          <t>“members of Penford’s management team provided a presentation to Party C regarding Penford’s operations” (p. 29)</t>
         </is>
       </c>
       <c r="R32" s="2" t="n"/>
       <c r="S32" s="2" t="n"/>
       <c r="T32" s="3" t="n">
-        <v>41911</v>
+        <v>41907</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>41911</v>
+        <v>41907</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>41911</v>
+        <v>41907</v>
       </c>
     </row>
     <row r="33">
@@ -2549,10 +2570,14 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Penford</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="n"/>
+          <t>Party F</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Other material event</t>
@@ -2566,20 +2591,22 @@
       </c>
       <c r="H33" s="2" t="n"/>
       <c r="I33" s="2" t="n"/>
-      <c r="J33" s="2" t="n"/>
-      <c r="K33" s="2" t="n"/>
-      <c r="L33" s="2" t="n"/>
-      <c r="M33" s="2" t="n"/>
-      <c r="N33" s="2" t="n"/>
-      <c r="O33" s="2" t="n"/>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr"/>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>Price requirement (internal): board wanted Ingredion's $18.25–$18.50 raised a further $0.50–$1.00 and approved further negotiation. Executive Committee disappointment (09/19) had been relayed to Ingredion 09/23.</t>
+          <t>Party F declines further discussions: not a suitable strategic fit. It never signed an NDA or entered, so no exit row. Counted among the two that declined NDAs.</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>the board indicated it would prefer to see the per share price increase by an additional $0.50 to $1.00 (p. 30)</t>
+          <t>“Party F communicated to Deutsche Bank that a combination with Penford was not a suitable strategic fit and declined to pursue further discussions regarding a transaction” (p. 30)</t>
         </is>
       </c>
       <c r="R33" s="2" t="n"/>
@@ -2626,22 +2653,22 @@
       </c>
       <c r="H34" s="2" t="n"/>
       <c r="I34" s="2" t="n"/>
-      <c r="J34" s="2" t="n"/>
-      <c r="K34" s="2" t="n"/>
-      <c r="L34" s="2" t="n"/>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N34" s="2" t="n"/>
-      <c r="O34" s="2" t="n"/>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr"/>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>NDA with standstill that falls away on announcement of a definitive sale agreement; Deutsche Bank sent information including historical results and financial projections. Party A's entry.</t>
+          <t>Party A’s entry: NDA with standstill that falls away on announcement of a definitive sale agreement. Deutsche Bank sends written information on operations, segments, historical financials and projections.</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>On September 30, 2014, Penford and Party A executed a nondisclosure and standstill agreement (p. 30)</t>
+          <t>“On September 30, 2014, Penford and Party A executed a nondisclosure and standstill agreement” (p. 30)</t>
         </is>
       </c>
       <c r="R34" s="2" t="n"/>
@@ -2688,22 +2715,22 @@
       </c>
       <c r="H35" s="2" t="n"/>
       <c r="I35" s="2" t="n"/>
-      <c r="J35" s="2" t="n"/>
-      <c r="K35" s="2" t="n"/>
-      <c r="L35" s="2" t="n"/>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N35" s="2" t="n"/>
-      <c r="O35" s="2" t="n"/>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr"/>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>Information access and price requirement: Deutsche Bank told Party A there would be no in-person management presentation unless its price looked competitive, likely over $20.00 per share (contrast Party C, #30; Ingredion, #13).</t>
+          <t>Information access and price requirement: Deutsche Bank tells Party A no in-person management presentation unless its price looks competitive, which would likely mean over $20.00 per share. Ingredion and Party C had presentations.</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>Penford would not provide in-person management presentations unless there was an indication that Party A’s proposed offer price would be competitive (p. 30)</t>
+          <t>“Penford would not provide in-person management presentations unless there was an indication that Party A’s proposed offer price would be competitive” (p. 30)</t>
         </is>
       </c>
       <c r="R35" s="2" t="n"/>
@@ -2732,7 +2759,7 @@
           <t>Penford</t>
         </is>
       </c>
-      <c r="D36" s="2" t="n"/>
+      <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Other material event</t>
@@ -2746,20 +2773,20 @@
       </c>
       <c r="H36" s="2" t="n"/>
       <c r="I36" s="2" t="n"/>
-      <c r="J36" s="2" t="n"/>
-      <c r="K36" s="2" t="n"/>
-      <c r="L36" s="2" t="n"/>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="n"/>
-      <c r="N36" s="2" t="n"/>
-      <c r="O36" s="2" t="n"/>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr"/>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>Price requirement: Deutsche Bank told J.P. Morgan the board was disappointed with $18.25–$18.50 and wanted at least $20.00 per share. On 10/02 Malkoski said the board wanted about $20.00 but would keep negotiating.</t>
+          <t>Price requirement to Ingredion: Deutsche Bank tells J.P. Morgan the board is disappointed with $18.25–$18.50 and wanted at least $20.00. Follows Malkoski’s 09/23 disappointment call and 09/29 board preference for $0.50–$1.00 more.</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>Deutsche Bank further explained that Penford’s board of directors had wanted a purchase price of at least $20.00 per share. (p. 30)</t>
+          <t>“Deutsche Bank further explained that Penford’s board of directors had wanted a purchase price of at least $20.00 per share.” (p. 30)</t>
         </is>
       </c>
       <c r="R36" s="2" t="n"/>
@@ -2828,16 +2855,16 @@
       <c r="M37" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N37" s="2" t="n"/>
-      <c r="O37" s="2" t="n"/>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr"/>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>Unclear: no condition stated; diligence meetings still continuing. Oral: Fortnum said Ingredion was prepared to move forward at $18.50 fully diluted, narrowing #26's range; Malkoski said unlikely to win a board recommendation.</t>
+          <t>No condition stated; diligence still open. Oral, on call: Ingredion “still struggling” to justify more but will move forward at $18.50 per fully diluted share, the top of #27. Malkoski: board wants about $20.00 but will keep negotiating; $18.50 unlikely enough.</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>Mr. Fortnum then stated that Ingredion was prepared to move forward based on a proposed price of $18.50 per share on a fully diluted basis. (p. 30)</t>
+          <t>“Mr. Fortnum then stated that Ingredion was prepared to move forward based on a proposed price of $18.50 per share on a fully diluted basis.” (p. 30)</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
@@ -2910,16 +2937,16 @@
       <c r="M38" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N38" s="2" t="n"/>
-      <c r="O38" s="2" t="n"/>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr"/>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>Unclear: no condition stated; year-end financials not yet delivered (#44). Letter, later same day, revising the indication of interest to $19.00 fully diluted; cash not stated. Ref: $12.77 close 10/01/2014; 49% premium.</t>
+          <t>No condition stated; diligence still open. Letter raising the indication to $19.00 per fully diluted share, same day as #36. Ref: $12.77 close 10/01/2014; 49% premium.</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>Penford received a letter from Ingredion regarding its indication of interest and increasing the proposed price to $19.00 per share (p. 30)</t>
+          <t>“Penford received a letter from Ingredion regarding its indication of interest and increasing the proposed price to $19.00 per share of outstanding Penford capital stock on a fully diluted basis” (p. 30)</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
@@ -2952,7 +2979,7 @@
           <t>Penford</t>
         </is>
       </c>
-      <c r="D39" s="2" t="n"/>
+      <c r="D39" s="2" t="inlineStr"/>
       <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Round opened</t>
@@ -2966,20 +2993,20 @@
       </c>
       <c r="H39" s="2" t="n"/>
       <c r="I39" s="2" t="n"/>
-      <c r="J39" s="2" t="n"/>
-      <c r="K39" s="2" t="n"/>
-      <c r="L39" s="2" t="n"/>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="n"/>
-      <c r="N39" s="2" t="n"/>
-      <c r="O39" s="2" t="n"/>
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr"/>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>Board directed management to negotiate and finalize a definitive agreement with Ingredion after Deutsche Bank said Party A was unlikely to reach $20.00 and no other contact would propose. Ingredion told same day; merger agreement drafts exchanged from 10/03.</t>
+          <t>Board directs management to negotiate and finalize a definitive agreement with Ingredion at $19.00; Ingredion told the same day. Deutsche Bank: Party A unlikely to reach $20.00, no other contact will propose; board considers but does not contact Party G. No due date set.</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>the directors present at the board meeting unanimously directed management to proceed to negotiate and finalize a definitive agreement with Ingredion (p. 31)</t>
+          <t>“the directors present at the board meeting unanimously directed management to proceed to negotiate and finalize a definitive agreement with Ingredion.” (p. 31)</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
@@ -3012,7 +3039,7 @@
           <t>Sidley Austin LLP</t>
         </is>
       </c>
-      <c r="D40" s="2" t="n"/>
+      <c r="D40" s="2" t="inlineStr"/>
       <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Adviser</t>
@@ -3026,20 +3053,20 @@
       </c>
       <c r="H40" s="2" t="n"/>
       <c r="I40" s="2" t="n"/>
-      <c r="J40" s="2" t="n"/>
-      <c r="K40" s="2" t="n"/>
-      <c r="L40" s="2" t="n"/>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="n"/>
-      <c r="N40" s="2" t="n"/>
-      <c r="O40" s="2" t="n"/>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr"/>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>Ingredion's legal counsel; earliest shown acting 10/03/2014, receiving Perkins Coie's revised draft merger agreement.</t>
+          <t>Ingredion’s legal counsel; earliest reported acting when Perkins Coie sends it a revised merger agreement draft on 10/03/2014.</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>Perkins Coie sent a revised draft of the merger agreement to Sidley Austin LLP (referred to as Sidley Austin), Ingredion’s legal counsel (p. 31)</t>
+          <t>“Sidley Austin LLP (referred to as Sidley Austin), Ingredion’s legal counsel” (p. 31)</t>
         </is>
       </c>
       <c r="R40" s="2" t="n"/>
@@ -3086,22 +3113,22 @@
       </c>
       <c r="H41" s="2" t="n"/>
       <c r="I41" s="2" t="n"/>
-      <c r="J41" s="2" t="n"/>
-      <c r="K41" s="2" t="n"/>
-      <c r="L41" s="2" t="n"/>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N41" s="2" t="n"/>
-      <c r="O41" s="2" t="n"/>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr"/>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>Valuation statement without offer: on Deutsche Bank follow-up, Party A said any offer would be below $17.50–$18.00 per share in cash; Deutsche Bank encouraged a letter of interest for the board. Party A not admitted to round 2.</t>
+          <t>Valuation statement without an offer: on Deutsche Bank follow-up, Party A says any offer would be below $17.50–$18.00 per share in cash. Deutsche Bank encourages it to submit a letter of interest for the board.</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>Party A indicated any offer would be below $17.50 - $18.00 per share in cash (p. 31)</t>
+          <t>“Party A indicated any offer would be below $17.50 - $18.00 per share in cash” (p. 31)</t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
@@ -3131,10 +3158,10 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Milbank, Tweed, Hadley &amp; McCloy, LLP</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="n"/>
+          <t>Milbank, Tweed, Hadley &amp; McCloy LLP</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr"/>
       <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Adviser</t>
@@ -3148,20 +3175,20 @@
       </c>
       <c r="H42" s="2" t="n"/>
       <c r="I42" s="2" t="n"/>
-      <c r="J42" s="2" t="n"/>
-      <c r="K42" s="2" t="n"/>
-      <c r="L42" s="2" t="n"/>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="n"/>
-      <c r="N42" s="2" t="n"/>
-      <c r="O42" s="2" t="n"/>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr"/>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>SEACOR's legal counsel; earliest shown acting 10/07/2014 when Perkins Coie raised Ingredion's request for a SEACOR voting and support agreement, which Milbank said was conceptually acceptable if it ended on termination for a superior offer.</t>
+          <t>Legal counsel to SEACOR (shareholder, not a bidder), contacted by Perkins Coie on Ingredion’s request for a SEACOR voting and support agreement; accepts the concept if it ends when the merger agreement is terminated for a superior offer.</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>Milbank, Tweed, Hadley &amp; McCloy, LLP (referred to as Milbank), legal counsel to SEACOR (p. 31)</t>
+          <t>“Milbank, Tweed, Hadley &amp; McCloy, LLP (referred to as Milbank), legal counsel to SEACOR” (p. 31)</t>
         </is>
       </c>
       <c r="R42" s="2" t="n"/>
@@ -3208,9 +3235,9 @@
       </c>
       <c r="H43" s="2" t="n"/>
       <c r="I43" s="2" t="n"/>
-      <c r="J43" s="2" t="n"/>
-      <c r="K43" s="2" t="n"/>
-      <c r="L43" s="2" t="n"/>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
       <c r="M43" s="2" t="n">
         <v>1</v>
       </c>
@@ -3219,15 +3246,15 @@
           <t>Not stated</t>
         </is>
       </c>
-      <c r="O43" s="2" t="n"/>
+      <c r="O43" s="2" t="inlineStr"/>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>Party D told Deutsche Bank at a meeting that it did not intend to move forward with discussions. No bid; no reason given. Round 1 is the round being left (not admitted to round 2).</t>
+          <t>At a meeting with Deutsche Bank, Party D says it does not intend to move forward; no reason given. Party D never bid.</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t>Party D, who indicated that it did not intend to move forward with discussions regarding a potential transaction involving the Company (p. 31)</t>
+          <t>“Party D, who indicated that it did not intend to move forward with discussions regarding a potential transaction involving the Company” (p. 31)</t>
         </is>
       </c>
       <c r="R43" s="2" t="n"/>
@@ -3248,15 +3275,19 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>10/10/2014</t>
+          <t>10/11/2014</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Penford</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="n"/>
+          <t>Ingredion</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Other material event</t>
@@ -3270,32 +3301,34 @@
       </c>
       <c r="H44" s="2" t="n"/>
       <c r="I44" s="2" t="n"/>
-      <c r="J44" s="2" t="n"/>
-      <c r="K44" s="2" t="n"/>
-      <c r="L44" s="2" t="n"/>
-      <c r="M44" s="2" t="n"/>
-      <c r="N44" s="2" t="n"/>
-      <c r="O44" s="2" t="n"/>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr"/>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>Projections revised after bidding began: Adjusted Strategic Plan, pushing growth targets out one year, provided to Deutsche Bank and used for its opinion. From projections section; filing does not say bidders received it.</t>
+          <t>Information access: Ingredion receives FY2014 draft financials below the Strategic Plan projections; reconciliation calls 10/11–12; on 10/13 Fortnum warns of possible adverse valuation impact. No other bidder reported receiving them. Adjusted Strategic Plan went only to Deutsche Bank (10/10, p. 43).</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>The Adjusted Strategic Plan was provided to Deutsche Bank on October 10, 2014. (p. 43)</t>
+          <t>“Penford provided Ingredion with draft financial statements for the fiscal year ended August 31, 2014 (referred to as the 2014 draft financial statements), which reflected lower volume, lower revenue” (p. 31)</t>
         </is>
       </c>
       <c r="R44" s="2" t="n"/>
       <c r="S44" s="2" t="n"/>
       <c r="T44" s="3" t="n">
-        <v>41922</v>
+        <v>41923</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>41922</v>
+        <v>41923</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>41922</v>
+        <v>41923</v>
       </c>
     </row>
     <row r="45">
@@ -3304,12 +3337,12 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>10/11/2014</t>
+          <t>10/13/2014</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Ingredion</t>
+          <t>Party A</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -3330,34 +3363,38 @@
       </c>
       <c r="H45" s="2" t="n"/>
       <c r="I45" s="2" t="n"/>
-      <c r="J45" s="2" t="n"/>
-      <c r="K45" s="2" t="n"/>
-      <c r="L45" s="2" t="n"/>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
       <c r="M45" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N45" s="2" t="n"/>
-      <c r="O45" s="2" t="n"/>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr"/>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>Information access: Penford gave Ingredion draft FY2014 financial statements showing lower volume, revenue and EBITDA than the strategic-plan projections; 10/13 Fortnum said this might hurt Ingredion's valuation. Not reported as given to Party A.</t>
+          <t>Valuation statement without an offer: Party A tells Deutsche Bank its value range fell from $17.50–$18.00 to $16.00–$18.00 per share, citing market volatility.</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>On October 11, 2014, Penford provided Ingredion with draft financial statements for the fiscal year ended August 31, 2014 (p. 31)</t>
-        </is>
-      </c>
-      <c r="R45" s="2" t="n"/>
+          <t>“its value range for a potential transaction had been reduced from $17.50 - $18.00 per share to $16.00 - $18.00 per share, due to increased volatility in the markets” (p. 32)</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
       <c r="S45" s="2" t="n"/>
       <c r="T45" s="3" t="n">
-        <v>41923</v>
+        <v>41925</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>41923</v>
+        <v>41925</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>41923</v>
+        <v>41925</v>
       </c>
     </row>
     <row r="46">
@@ -3366,12 +3403,12 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>10/13/2014</t>
+          <t>10/14/2014</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Party A</t>
+          <t>Ingredion</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -3381,7 +3418,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Bid reaffirmed</t>
         </is>
       </c>
       <c r="F46" s="2" t="n">
@@ -3390,40 +3427,56 @@
       <c r="G46" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H46" s="2" t="n"/>
-      <c r="I46" s="2" t="n"/>
-      <c r="J46" s="2" t="n"/>
-      <c r="K46" s="2" t="n"/>
-      <c r="L46" s="2" t="n"/>
+      <c r="H46" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="I46" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="M46" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N46" s="2" t="n"/>
-      <c r="O46" s="2" t="n"/>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr"/>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>Valuation statement without offer: Party A told Deutsche Bank its value range fell from $17.50–$18.00 to $16.00–$18.00 per share, citing market volatility.</t>
+          <t>Ready to sign: wants to “promptly enter into” the agreement; no financing condition, cash and revolver funding (p. 45). Carried from #37: Fortnum confirms $19.00 despite weaker draft financials while finalizing. Cash per final agreement (p. 2).</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>its value range for a potential transaction had been reduced from $17.50 - $18.00 per share to $16.00 - $18.00 per share (p. 32)</t>
+          <t>“Mr. Fortnum called Mr. Malkoski to confirm the proposed price of $19.00 and discuss finalizing the draft merger agreement and proceeding with the transaction as previously planned.” (p. 32)</t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>Q5</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="S46" s="2" t="n"/>
       <c r="T46" s="3" t="n">
-        <v>41925</v>
+        <v>41926</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>41925</v>
+        <v>41926</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>41925</v>
+        <v>41926</v>
       </c>
     </row>
     <row r="47">
@@ -3437,7 +3490,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Ingredion</t>
+          <t>Party A</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -3447,7 +3500,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Bid reaffirmed</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F47" s="2" t="n">
@@ -3457,44 +3510,44 @@
         <v>2</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not stated</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>Formal</t>
+          <t>Informal</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Unclear</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N47" s="2" t="n"/>
-      <c r="O47" s="2" t="n"/>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr"/>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>None: ready to sign; no financing condition (cash and revolver), diligence complete. Fortnum confirmed $19.00 (carried from #37) despite weaker draft financials and asked to finalize the agreement. Agreement adds a year-end financials closing condition.</t>
+          <t>Conditions not reported. “Formal letter” indication of interest at $16.00 per share, lowered for market volatility; no draft agreement or markup reported. Answers Deutsche Bank’s 10/04 request; received “later on” 10/14. Ref: $11.07 close 10/13/2014; 45% premium.</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
         <is>
-          <t>Mr. Fortnum called Mr. Malkoski to confirm the proposed price of $19.00 and discuss finalizing the draft merger agreement (p. 32)</t>
+          <t>“Party A provided a formal letter with its indication of interest with respect to an acquisition of the Company at a price of $16.00 per share” (p. 32)</t>
         </is>
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>Q6</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="S47" s="2" t="n"/>
@@ -3514,12 +3567,12 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>10/14/2014</t>
+          <t>10/14/2014 (evening)</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Party A</t>
+          <t>Ingredion</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -3529,7 +3582,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Merger agreement signed</t>
         </is>
       </c>
       <c r="F48" s="2" t="n">
@@ -3538,47 +3591,27 @@
       <c r="G48" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H48" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="I48" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
+      <c r="H48" s="2" t="n"/>
+      <c r="I48" s="2" t="n"/>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
       <c r="M48" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N48" s="2" t="n"/>
-      <c r="O48" s="2" t="n"/>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr"/>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>Unclear: no conditions reported; Party A never had a management presentation. Formal letter of interest at $16.00, lowered for market volatility; cash not stated. Received, not admitted to round 2. Ref: $11.07 close 10/13/2014; 45% premium.</t>
+          <t>$19.00 cash per share via Prospect Sub, Inc.; options cashed out at spread. Board approved after Deutsche Bank fairness opinion. SEACOR signs voting and support agreement. No go-shop; no-shop with fiduciary out; $7.6 million termination fee.</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>Party A provided a formal letter with its indication of interest with respect to an acquisition of the Company at a price of $16.00 per share (p. 32)</t>
-        </is>
-      </c>
-      <c r="R48" s="2" t="inlineStr">
-        <is>
-          <t>Q5</t>
-        </is>
-      </c>
+          <t>“During the evening on October 14, 2014, Penford and Ingredion finalized and executed the merger agreement” (p. 33)</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="n"/>
       <c r="S48" s="2" t="n"/>
       <c r="T48" s="3" t="n">
         <v>41926</v>
@@ -3601,7 +3634,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Ingredion</t>
+          <t>Party A</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -3611,7 +3644,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Merger agreement signed</t>
+          <t>Not selected at signing</t>
         </is>
       </c>
       <c r="F49" s="2" t="n">
@@ -3622,25 +3655,37 @@
       </c>
       <c r="H49" s="2" t="n"/>
       <c r="I49" s="2" t="n"/>
-      <c r="J49" s="2" t="n"/>
-      <c r="K49" s="2" t="n"/>
-      <c r="L49" s="2" t="n"/>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
       <c r="M49" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N49" s="2" t="n"/>
-      <c r="O49" s="2" t="n"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>Lower offer than rivals</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>Signed evening of 10/14/2014 after unanimous board approval and Deutsche Bank's fairness opinion: $19.00 per share in cash through Prospect Sub, Inc.; no financing condition; $7.6 million termination fee.</t>
+          <t>Inferred: Party A bid $16.00 the same day and was still live when Penford signed with Ingredion at $19.00. Board reasons say the market check produced no indication at or above $19.00.</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
         <is>
-          <t>During the evening on October 14, 2014, Penford and Ingredion finalized and executed the merger agreement (p. 33)</t>
-        </is>
-      </c>
-      <c r="R49" s="2" t="n"/>
+          <t>“which did not include any non-binding indications of interest of equal to or more than the $19.00 per share agreed upon with Ingredion” (p. 33)</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
       <c r="S49" s="2" t="n"/>
       <c r="T49" s="3" t="n">
         <v>41926</v>
@@ -3658,51 +3703,69 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>10/14/2014</t>
+          <t>by 10/14/2014</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>SEACOR</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="n"/>
+          <t>Party C</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Not selected at signing</t>
         </is>
       </c>
       <c r="F50" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H50" s="2" t="n"/>
       <c r="I50" s="2" t="n"/>
-      <c r="J50" s="2" t="n"/>
-      <c r="K50" s="2" t="n"/>
-      <c r="L50" s="2" t="n"/>
-      <c r="M50" s="2" t="n"/>
-      <c r="N50" s="2" t="n"/>
-      <c r="O50" s="2" t="n"/>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>Voting support: SEACOR (about 9.28%) signed a voting and support agreement with Ingredion and Penford to vote for the merger and not solicit proxies for its nominees until termination, adverse amendment or 03/15/2015.</t>
+          <t>Inferred: last seen at its 09/25 presentation, never mentioned again, no bid reported. Deutsche Bank’s summary puts it among three NDA signers that “did not move forward in a timely manner or made a lower indication of value”.</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>Penford, Ingredion and SEACOR executed the voting and support agreement (p. 33)</t>
-        </is>
-      </c>
-      <c r="R50" s="2" t="n"/>
+          <t>“the remaining three of which either did not move forward in a timely manner or made a lower indication of value” (p. 32)</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
+      </c>
       <c r="S50" s="2" t="n"/>
       <c r="T50" s="3" t="n">
         <v>41926</v>
       </c>
       <c r="U50" s="3" t="n">
-        <v>41926</v>
+        <v>41907</v>
       </c>
       <c r="V50" s="3" t="n">
         <v>41926</v>
@@ -3714,200 +3777,60 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>10/14/2014</t>
+          <t>10/15/2014</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Party A</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Penford</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr"/>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Not selected at signing</t>
+          <t>Merger announced</t>
         </is>
       </c>
       <c r="F51" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G51" s="2" t="n">
-        <v>2</v>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
       </c>
       <c r="H51" s="2" t="n"/>
       <c r="I51" s="2" t="n"/>
-      <c r="J51" s="2" t="n"/>
-      <c r="K51" s="2" t="n"/>
-      <c r="L51" s="2" t="n"/>
-      <c r="M51" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N51" s="2" t="inlineStr">
-        <is>
-          <t>Lower offer than rivals</t>
-        </is>
-      </c>
-      <c r="O51" s="2" t="n"/>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="n"/>
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr"/>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>Still live when Penford signed with Ingredion at $19.00; its $16.00 letter (#47) was lower. Deutsche Bank's 10/14 report grouped A, C, D as not moving forward in time or giving a lower value.</t>
+          <t>Penford and Ingredion issue press releases before market open.</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
         <is>
-          <t>the remaining three of which either did not move forward in a timely manner or made a lower indication of value (p. 32)</t>
-        </is>
-      </c>
-      <c r="R51" s="2" t="inlineStr">
-        <is>
-          <t>Q7</t>
-        </is>
-      </c>
+          <t>“Penford and Ingredion issued press releases announcing the transaction on October 15, 2014 prior to the opening of trading.” (p. 33)</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="n"/>
       <c r="S51" s="2" t="n"/>
       <c r="T51" s="3" t="n">
-        <v>41926</v>
+        <v>41927</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>41926</v>
+        <v>41927</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>41926</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>by 10/14/2014</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>Party C</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>Not selected at signing</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G52" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H52" s="2" t="n"/>
-      <c r="I52" s="2" t="n"/>
-      <c r="J52" s="2" t="n"/>
-      <c r="K52" s="2" t="n"/>
-      <c r="L52" s="2" t="n"/>
-      <c r="M52" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N52" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="O52" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="P52" s="2" t="inlineStr">
-        <is>
-          <t>Inferred: last reported at its 09/25 presentation, under NDA; no proposal (per 10/03 report) and no exit reported. Deutsche Bank's 10/14 summary places it among parties that did not move forward in a timely manner or bid lower.</t>
-        </is>
-      </c>
-      <c r="Q52" s="2" t="inlineStr">
-        <is>
-          <t>no other companies that had been contacted during the market check process indicated they would provide a proposal or other indication of interest (p. 30)</t>
-        </is>
-      </c>
-      <c r="R52" s="2" t="inlineStr">
-        <is>
-          <t>Q7</t>
-        </is>
-      </c>
-      <c r="S52" s="2" t="n"/>
-      <c r="T52" s="3" t="n">
-        <v>41926</v>
-      </c>
-      <c r="U52" s="2" t="n"/>
-      <c r="V52" s="2" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>10/15/2014</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>Penford</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="n"/>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>Merger announced</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="n"/>
-      <c r="I53" s="2" t="n"/>
-      <c r="J53" s="2" t="n"/>
-      <c r="K53" s="2" t="n"/>
-      <c r="L53" s="2" t="n"/>
-      <c r="M53" s="2" t="n"/>
-      <c r="N53" s="2" t="n"/>
-      <c r="O53" s="2" t="n"/>
-      <c r="P53" s="2" t="inlineStr">
-        <is>
-          <t>Penford and Ingredion issued press releases before market open.</t>
-        </is>
-      </c>
-      <c r="Q53" s="2" t="inlineStr">
-        <is>
-          <t>Penford and Ingredion issued press releases announcing the transaction on October 15, 2014 prior to the opening of trading. (p. 33)</t>
-        </is>
-      </c>
-      <c r="R53" s="2" t="n"/>
-      <c r="S53" s="2" t="n"/>
-      <c r="T53" s="3" t="n">
         <v>41927</v>
       </c>
-      <c r="U53" s="3" t="n">
-        <v>41927</v>
-      </c>
-      <c r="V53" s="3" t="n">
-        <v>41927</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V53"/>
+  <autoFilter ref="A1:V51"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3924,13 +3847,13 @@
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
-    <col width="45" customWidth="1" min="10" max="10"/>
+    <col width="45" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3997,12 +3920,12 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Deutsche Bank market-check outreach to six strategic counterparties, early-to-mid September 2014 (first contacts reported 09/09), carrying out the board’s 08/28 authorization (#16).</t>
+          <t>Deutsche Bank market-check outreach to strategic counterparties (#18), executing the 08/28 board authorization; Ingredion negotiating and in diligence in parallel.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>4 strategic: Ingredion (carried from round 0, in diligence), Party C (NDA 09/15), Party D (NDA 09/23), Party A (NDA 09/30). Parties B, E and F were contacted but never entered.</t>
+          <t>4 Strategic: Ingredion (carried from round 0), Party C (NDA 09/15), Party D (NDA 09/23), Party A (NDA 09/30). Contacted but never entered: Parties B, E, F.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -4022,12 +3945,12 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>1: Ingredion (09/17 $18.25–$18.50 oral; 10/02 $18.50 oral; 10/02 $19.00 letter). No proposal from Parties A, C or D in the round.</t>
+          <t>1: Ingredion ($18.25–$18.50 on 09/17, #27; $18.50 and $19.00 on 10/02, #36, #37).</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>10/03: Ingredion selected for definitive negotiation (one advanced). Party A still being received (round 2). Party D withdrew 10/08; Party C inferred not selected at signing.</t>
+          <t>Ingredion advanced alone to definitive negotiation (10/03). A, C and D were not admitted but not excluded: D withdrew 10/08; C stayed open until signing; A kept being solicited (see round 2).</t>
         </is>
       </c>
     </row>
@@ -4043,12 +3966,12 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Board directed management to negotiate and finalize a definitive agreement with Ingredion (#38).</t>
+          <t>Board directs management to negotiate and finalize a definitive agreement with Ingredion (#38).</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>1 strategic: Ingredion. Then, still being received, not admitted: Party A (strategic).</t>
+          <t>1 Strategic: Ingredion. Still being received, not admitted: Party A (Strategic).</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -4068,12 +3991,12 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2: Ingredion (10/14 reaffirmed $19.00), Party A (10/14 $16.00 letter).</t>
+          <t>2: Ingredion (reaffirmed $19.00 on 10/14, #45); Party A ($16.00 on 10/14, #46, not admitted).</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>signing with Ingredion 10/14/2014 at $19.00 cash; Party A not selected.</t>
+          <t>Signing with Ingredion at $19.00 cash on 10/14/2014; Party A (#48) and Party C (from round 1, #49) not selected at signing.</t>
         </is>
       </c>
     </row>
@@ -4093,11 +4016,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -4146,27 +4069,27 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Ingredion’s first price: on 07/17 Gordon cited no number, but the 09/29 board minutes call $16.00 (the 52-week high) Ingredion’s “initial indication”. Is 07/17 a Bid, and is the 08/06 $17.00 suggestion a Bid?</t>
+          <t>Are Ingredion’s early price references bids? On 07/19 Fortnum said $16.00 would be a challenge. On 08/06 he said $17.00 “could likely get support”. On 09/29 the board called $16.00 Ingredion’s “initial indication”.</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Record 07/17 as Bidder interest (no price) and 08/06 $17.00 as the first, oral, Informal Bid.</t>
+          <t>Record 08/06 as an informal $17.00 Bid: Ingredion said it was ready to propose, and Penford answered it as a proposed price. Keep 07/19 as a valuation statement: no offer was made, and the $16.00 is the 52-week high.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Gordon “did not cite a specific number” (p. 24); Fortnum said Ingredion was “prepared to submit a proposal” and suggested $17.00 (p. 25); board’s “$16.00 (based on the 52-week high)” (p. 30).</t>
+          <t>P. 24 (“did not discuss a potential purchase price”); p. 25 (“proposed price would probably not be high enough”); p. 30 (“initial indication of $16.00 (based on the 52-week high)”).</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>#2, #6</t>
+          <t>#3, #7</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>A $16.00 Bid on 07/17 would add a round-0 bid; dropping #6 would make the 08/10 $18.00 letter the first price.</t>
+          <t>As a $16.00 bid, the 07/19 row becomes Ingredion’s first bid, giving a path of $16→$17→$18→$18.25–18.50→$18.50→$19. Dropping the 08/06 bid removes the $17.00 step.</t>
         </is>
       </c>
       <c r="G2" s="2" t="n"/>
@@ -4179,27 +4102,27 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Process and round map: one process; round 0 (Ingredion approach through the 08/28 decision), round 1 opened by the market-check outreach, round 2 opened 10/03 by definitive negotiation with Ingredion; announcement post. Is this the right map?</t>
+          <t>Process and round map: one process; round 0 to the start of Deutsche Bank’s outreach; round 1 = market check with Ingredion negotiating in parallel; round 2 = definitive negotiation with Ingredion from 10/03. Is round 1 correctly opened at the outreach rather than at 08/14?</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Yes. One process, rounds 0, 1, 2 as recorded. No bid due date was set in either round, so no deadline-outcome Question arises.</t>
+          <t>Keep. E6 puts the first outreach wave first; outreach cannot be shown to start within a week of the 08/28 authorization, so the wave itself opens round 1. Round 2 opens at the 10/03 move to definitive negotiation (no round announced as final).</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>E6 opens round 1 at the first outreach wave (p. 28); 10/03 board direction to finalize with Ingredion is a move to definitive negotiation (p. 31). Contacts run continuously 07/08–10/14/2014; no gap of about two months. E5: only one attempt; the 2007 and 2009 approaches are year-dated only (p. 23), so they go to Deal facts, and tests (a)–(c) never trigger a second process.</t>
+          <t>Outreach “early- to mid-September” (p. 28); definitive-negotiation direction 10/03 (p. 31). E5: (a) never met: Ingredion in negotiation throughout; (b) not met: no gap of ~2 months or more between 07/08 and 10/14/2014; (c) not tested. The 2007/2009 approaches are dated only by year (p. 23).</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>#16, #26, #38</t>
+          <t>#11, #12, #13, #14, #16, #17, #18, #38</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Alternatives: round 1 opens 08/14 (target admits Ingredion to diligence) moving #11–#15 into round 1; or 08/28 decision date; or Ingredion’s 09/17 and 10/02 bids stay round-0 bargaining over #7, moving #26, #36, #37 to round 0.</t>
+          <t>Alternative: open round 1 on 08/14, when the target began substantive bilateral negotiation with Ingredion. That moves the five Ingredion/target rows dated 08/14–08/28 from round 0 to round 1 and the round-opened row back to 08/14; the $17.00 and $18.00 bids stay in round 0.</t>
         </is>
       </c>
       <c r="G3" s="2" t="n"/>
@@ -4212,27 +4135,27 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Outreach total: the filing says Deutsche Bank contacted six strategic parties “throughout early- to mid-September”, but Party F was contacted 09/24. Who are the six?</t>
+          <t>The filing says six counterparties were contacted “throughout early- to mid-September”, but Party F was contacted only on 09/24, and the 10/14 total is also six. Is there a seventh, unnamed contact?</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>The six are Parties A–F. The 10/14 breakdown (two declined NDAs, one unanswered voicemail, three remaining) fits B and F, E, and A, C, D exactly.</t>
+          <t>No. Treat the six as Parties A–F. The 10/14 breakdown fits A–F exactly: B and F declined NDAs, E never replied, and A, C and D signed NDAs.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>p. 28 (six contacted early-to-mid September); p. 29 (Party F contacted 09/24); p. 32 (total of six, with breakdown).</t>
+          <t>P. 28 (six in early–mid September); p. 29 (F contacted 09/24); p. 32 (total of six: two declined NDAs, one no reply, three remaining).</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>#16, #19, #20, #21, #22, #24, #29</t>
+          <t>#18, #20, #21, #22, #23, #25, #30</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>If the September six exclude F, a seventh unnamed contact exists, contradicting the stated total of six; one Contact row (Count 1, Unknown type) would be added. The auction screen (4 NDA parties) is unaffected.</t>
+          <t>If the September six excluded F, there were seven contacts, including one unnamed Strategic contact that never entered. Add one Contact row; entries, the auction screen and live counts would be unchanged.</t>
         </is>
       </c>
       <c r="G4" s="2" t="n"/>
@@ -4245,27 +4168,27 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Ingredion’s adviser delivered its own draft merger agreement on 09/06 while the $18.00 indication stood. Does that make Ingredion’s 09/17 and 10/02 bids Formal under E11(1)?</t>
+          <t>Should Ingredion’s round-1 bids be Formal? Ingredion sent its own draft merger agreement on 09/06, before its 09/17 and 10/02 price moves, and sent a markup on 10/08.</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>No; keep them Informal. The draft was not put forward with or expressly in support of those prices, and the filing calls them revised indications of interest.</t>
+          <t>Keep them Informal. The 09/06 draft came with no price and was not expressly tied to a proposal (E11 test 1). Formality is recorded at the 10/14 reaffirmation.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Draft delivered 09/06 (p. 28); 09/17 “could potentially increase” (p. 29); 10/02 letter “regarding its indication of interest” (p. 30).</t>
+          <t>P. 28 (J.P. Morgan provides initial draft merger agreement 09/06); p. 31 (Sidley revised draft 10/08); the 09/17 and 10/02 prices are called indications of interest (pp. 29–30).</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>#18, #26, #36, #37</t>
+          <t>#27, #36, #37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Three Ingredion bids in round 1 become Formal (Conditions stay Unclear), so round 1 would contain formal bids and Ingredion would not need the reaffirmation row (#46).</t>
+          <t>If Formal, Ingredion’s last three priced rows become Formal (Conditions Unclear), and the 10/14 row loses its purpose as a reaffirmation.</t>
         </is>
       </c>
       <c r="G5" s="2" t="n"/>
@@ -4278,27 +4201,27 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Party A’s 10/04 statement (any offer below $17.50–$18.00, cash) and 10/13 reduced value range ($16.00–$18.00): Bids, or valuation statements without an offer?</t>
+          <t>Party A’s 10/04 (“below $17.50–$18.00”) and 10/13 (“$16.00–$18.00 range”) statements: bids or valuation statements? Is its 10/14 letter correctly placed in round 2 as a bid received but not admitted?</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Valuation statements (Other material event). Party A’s first proposal is its 10/14 “formal letter with its indication of interest” at $16.00, which Deutsche Bank had asked for on 10/04.</t>
+          <t>Valuation statements. Only the 10/14 letter is an indication of interest. Place A in round 2 as “still being received, not admitted”, since the letter answers Deutsche Bank’s 10/04 request made after round 2 opened.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>p. 31 (“any offer would be below”; Deutsche Bank “encouraged Party A to submit a letter of interest”); p. 32 (value range reduced; formal letter at $16.00).</t>
+          <t>P. 31 (“any offer would be below”); p. 32 (“value range … reduced”; “formal letter with its indication of interest … $16.00”).</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>#40, #45, #47</t>
+          <t>#40, #44, #46, #48</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Party A would gain two Informal bids in round 2: 10/13 with Price low 16.00 and Price high 18.00; 10/04 with no clean endpoint (Price high blank or 17.50–18.00 read as a ceiling).</t>
+          <t>As bids, add a Bid row with Price high $18.00 (10/04, one-sided) and a $16.00–$18.00 Bid (10/13). Placing A’s rows in round 1 would leave round 2 with one bidder.</t>
         </is>
       </c>
       <c r="G6" s="2" t="n"/>
@@ -4311,27 +4234,27 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Should Ingredion’s 10/14 confirmation of $19.00 be a Bid reaffirmed row?</t>
+          <t>Is the 10/14 confirmation of $19.00 a Bid reaffirmed (Formal)?</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Yes. Fortnum himself confirmed the price after the board moved to finalize with Ingredion (10/03), and its latest priced row (#37) is Informal, so the row adds Ingredion’s only Formal price.</t>
+          <t>Yes. Ingredion itself confirmed its standing $19.00 price while the agreement was being finalized with it, after weaker draft financials had raised a repricing risk. Its latest priced row (#37) is Informal.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Fortnum “called Mr. Malkoski to confirm the proposed price of $19.00” (p. 32); board told price “remained at $19.00” (p. 32).</t>
+          <t>P. 32: Fortnum called “to confirm the proposed price of $19.00”; the board was told the price “remained at $19.00”.</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>#46</t>
+          <t>#45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Without it, Ingredion has no Formal bid; signing (#48) would be the only record of a binding $19.00 commitment.</t>
+          <t>If it is folded into the signing row, Ingredion’s last bid stays Informal and the winning offer never shows as Formal in the ledger.</t>
         </is>
       </c>
       <c r="G7" s="2" t="n"/>
@@ -4344,27 +4267,27 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>How do Party C and Party A leave? Neither has a reported exit.</t>
+          <t>Party C’s exit: Not selected at signing (inferred) or an earlier drop or withdrawal?</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Party C: inferred Not selected at signing, reason Not stated. Party A: Not selected at signing, Lower offer than rivals ($16.00 vs $19.00), not inferred since both offers are reported at signing.</t>
+          <t>Keep inferred Not selected at signing by 10/14. The filing never reports C withdrawing or being excluded, and the market check stayed open after 10/03 (A was pursued; D met Deutsche Bank on 10/08).</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Deutsche Bank kept the market check running after 10/03 (Party A 10/04, Party D 10/08; p. 31), so 10/03 did not drop them. 10/14 report: remaining three “did not move forward in a timely manner or made a lower indication of value” (p. 32).</t>
+          <t>P. 29 (last individual mention, 09/25 presentation); p. 30 (10/03: no other contact indicated a proposal); p. 32 (three “did not move forward in a timely manner or made a lower indication”).</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>#50, #51</t>
+          <t>#49</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Party C could instead be Dropped by target at 10/03 (round 1 advancement) or Withdrew (did not move forward); either changes the live count in round 2 and the exit’s valuation signal.</t>
+          <t>As Dropped by target on 10/03, C leaves before round 2 and the live count at signing falls from 2 to 1 (Ingredion, A). As Withdrew, the exit reason is still Not stated.</t>
         </is>
       </c>
       <c r="G8" s="2" t="n"/>
@@ -4384,7 +4307,7 @@
   <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="110" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -4408,7 +4331,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Penford Corporation (Washington corporation; specialty natural-based ingredients, Centennial, Colorado)</t>
+          <t>Penford Corporation (Washington corporation; Centennial, Colorado; NASDAQ Global Market)</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4355,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Strategic: global manufacturer and supplier of starch and sweetener ingredients (pp. 1, 18).</t>
+          <t>Strategic (global manufacturer and supplier of starch and sweetener ingredients, p. 1)</t>
         </is>
       </c>
     </row>
@@ -4444,7 +4367,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>$19.00 per share in cash, without interest; no financing condition, funded from available cash and revolver borrowings (p. 45). SEACOR (about 9.28%) voting and support agreement.</t>
+          <t>$19.00 per share in cash, without interest; options cashed out at the spread over exercise price. No financing condition; Ingredion to fund from available cash and revolving credit borrowings (pp. 2–3, 45).</t>
         </is>
       </c>
     </row>
@@ -4456,7 +4379,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>10/14/2014</t>
+          <t>10/14/2014 (evening)</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4391,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>10/15/2014 (press releases before market open)</t>
+          <t>10/15/2014, press releases before the opening of trading</t>
         </is>
       </c>
     </row>
@@ -4528,7 +4451,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>2007 and 2009: unsolicited indications of interest from two industry parties; confidentiality agreements and discussions, no offers (p. 23). Year-dated only, so no process rows.</t>
+          <t>In 2007 and 2009 two industry parties made unsolicited indications of interest; Penford signed a confidentiality agreement with each and exchanged information, but neither made an offer. Dated only to the year, so they get no rows (p. 23).</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4487,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>US dollars per share; Ingredion’s prices on a fully diluted basis.</t>
+          <t>US dollars per share of Penford common stock, generally stated on a fully diluted basis</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4523,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Ingredion’s CEO approached Penford in July 2014, amid SEACOR’s board nomination contest, and moved from an oral $17.00 suggestion to an $18.00 cash indication on 08/10. The board called that inadequate, refused exclusivity and gave Ingredion diligence access to win a higher price, while Deutsche Bank ran a market check of six strategic parties from September. Parties A, C and D signed NDAs; B and F declined, E never answered, and the board chose not to approach Party G. Ingredion edged up to $18.25–$18.50 and then $19.00 on 10/02, against the board’s wish for $20.00, and the board directed a definitive agreement on 10/03. Party D withdrew and Party A offered only $16.00, and Penford signed with Ingredion at $19.00 cash on 10/14/2014, with SEACOR’s voting support.</t>
+          <t>Ingredion approached Penford’s CEO in July 2014 while activist shareholder SEACOR was running a director slate. It bid $17.00 orally and then $18.00 in writing in August. Penford declined exclusivity and gave Ingredion a management presentation, a dataroom and site visits to push its price up. Deutsche Bank’s September market check contacted six strategic companies; Parties A, C and D signed NDAs and B, E and F dropped away. Ingredion rose to $18.25–$18.50 and then $19.00 after Penford asked for at least $20.00, and on 10/03 the board moved to definitive negotiation with Ingredion. Party D withdrew, Party A bid only $16.00, and Penford signed with Ingredion at $19.00 cash on 10/14/2014.</t>
         </is>
       </c>
     </row>
